--- a/Image_Classification_Papers_Ranking_2021_2026.xlsx
+++ b/Image_Classification_Papers_Ranking_2021_2026.xlsx
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -8299,6 +8299,748 @@
       <c r="O100" s="13" t="inlineStr">
         <is>
           <t>https://github.com/mboudiaf/TIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>Interpretable Image Classification via Non-parametric Part P</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="n"/>
+      <c r="H101" s="12" t="n"/>
+      <c r="I101" s="12" t="n"/>
+      <c r="J101" s="12" t="n"/>
+      <c r="K101" s="12" t="n"/>
+      <c r="L101" s="12" t="n"/>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Interpretable Image Classification via Non-parametric Part Prototype Learning</t>
+        </is>
+      </c>
+      <c r="N101" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhu_Interpretable_Image_Classification_via_Non-parametric_Part_Prototype_Learning_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O101" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>No Pains, More Gains</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="n"/>
+      <c r="H102" s="12" t="n"/>
+      <c r="I102" s="12" t="n"/>
+      <c r="J102" s="12" t="n"/>
+      <c r="K102" s="12" t="n"/>
+      <c r="L102" s="12" t="n"/>
+      <c r="M102" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。No Pains, More Gains: Recycling Sub-Salient Patches for Efficient High-Resolution Image Recognition</t>
+        </is>
+      </c>
+      <c r="N102" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Qin_No_Pains_More_Gains_Recycling_Sub-Salient_Patches_for_Efficient_High-Resolution_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O102" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>Beyond Image Classification</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G103" s="12" t="n"/>
+      <c r="H103" s="12" t="n"/>
+      <c r="I103" s="12" t="n"/>
+      <c r="J103" s="12" t="n"/>
+      <c r="K103" s="12" t="n"/>
+      <c r="L103" s="12" t="n"/>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Image Classification: A Video Benchmark and Dual-Branch Hybrid Discrimination Framework for Compositional Zero-Shot Learning</t>
+        </is>
+      </c>
+      <c r="N103" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Jiang_Beyond_Image_Classification_A_Video_Benchmark_and_Dual-Branch_Hybrid_Discrimination_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O103" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>MExD</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G104" s="12" t="n"/>
+      <c r="H104" s="12" t="n"/>
+      <c r="I104" s="12" t="n"/>
+      <c r="J104" s="12" t="n"/>
+      <c r="K104" s="12" t="n"/>
+      <c r="L104" s="12" t="n"/>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MExD: An Expert-Infused Diffusion Model for Whole-Slide Image Classification</t>
+        </is>
+      </c>
+      <c r="N104" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zhao_MExD_An_Expert-Infused_Diffusion_Model_for_Whole-Slide_Image_Classification_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O104" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>Few-Shot Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>Text Augmented Correlation Transformer For Few-shot Classifi</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="n"/>
+      <c r="H105" s="12" t="n"/>
+      <c r="I105" s="12" t="n"/>
+      <c r="J105" s="12" t="n"/>
+      <c r="K105" s="12" t="n"/>
+      <c r="L105" s="12" t="n"/>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Text Augmented Correlation Transformer For Few-shot Classification &amp;amp; Segmentation</t>
+        </is>
+      </c>
+      <c r="N105" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Nandam_Text_Augmented_Correlation_Transformer_For_Few-shot_Classification__Segmentation_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O105" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>Fast and Accurate Gigapixel Pathological Image Classificatio</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G106" s="12" t="n"/>
+      <c r="H106" s="12" t="n"/>
+      <c r="I106" s="12" t="n"/>
+      <c r="J106" s="12" t="n"/>
+      <c r="K106" s="12" t="n"/>
+      <c r="L106" s="12" t="n"/>
+      <c r="M106" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Fast and Accurate Gigapixel Pathological Image Classification with Hierarchical Distillation Multi-Instance Learning</t>
+        </is>
+      </c>
+      <c r="N106" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Dong_Fast_and_Accurate_Gigapixel_Pathological_Image_Classification_with_Hierarchical_Distillation_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O106" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>Explaining Domain Shifts in Language</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2025</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G107" s="12" t="n"/>
+      <c r="H107" s="12" t="n"/>
+      <c r="I107" s="12" t="n"/>
+      <c r="J107" s="12" t="n"/>
+      <c r="K107" s="12" t="n"/>
+      <c r="L107" s="12" t="n"/>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Explaining Domain Shifts in Language: Concept Erasing for Interpretable Image Classification</t>
+        </is>
+      </c>
+      <c r="N107" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2025/html/Zeng_Explaining_Domain_Shifts_in_Language_Concept_Erasing_for_Interpretable_Image_CVPR_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O107" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>Unconstrained Open Vocabulary Image Classification</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G108" s="12" t="n"/>
+      <c r="H108" s="12" t="n"/>
+      <c r="I108" s="12" t="n"/>
+      <c r="J108" s="12" t="n"/>
+      <c r="K108" s="12" t="n"/>
+      <c r="L108" s="12" t="n"/>
+      <c r="M108" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Unconstrained Open Vocabulary Image Classification: Zero-Shot Transfer from Text to Image via CLIP Inversion</t>
+        </is>
+      </c>
+      <c r="N108" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Allgeuer_Unconstrained_Open_Vocabulary_Image_Classification_Zero-Shot_Transfer_from_Text_to_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O108" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>CAMEL</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="n"/>
+      <c r="H109" s="12" t="n"/>
+      <c r="I109" s="12" t="n"/>
+      <c r="J109" s="12" t="n"/>
+      <c r="K109" s="12" t="n"/>
+      <c r="L109" s="12" t="n"/>
+      <c r="M109" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。CAMEL: Confidence-Aware Multi-Task Ensemble Learning with Spatial Information for Retina OCT Image Classification and Segmentation</t>
+        </is>
+      </c>
+      <c r="N109" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Jung_CAMEL_Confidence-Aware_Multi-Task_Ensemble_Learning_with_Spatial_Information_for_Retina_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O109" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>Pixel-Wise Shuffling with Collaborative Sparsity for Melanom</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="n"/>
+      <c r="H110" s="12" t="n"/>
+      <c r="I110" s="12" t="n"/>
+      <c r="J110" s="12" t="n"/>
+      <c r="K110" s="12" t="n"/>
+      <c r="L110" s="12" t="n"/>
+      <c r="M110" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Pixel-Wise Shuffling with Collaborative Sparsity for Melanoma Hyperspectral Image Classification</t>
+        </is>
+      </c>
+      <c r="N110" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Ekong_Pixel-Wise_Shuffling_with_Collaborative_Sparsity_for_Melanoma_Hyperspectral_Image_Classification_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O110" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data Augmentation for Image Classification using Generative </t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G111" s="12" t="n"/>
+      <c r="H111" s="12" t="n"/>
+      <c r="I111" s="12" t="n"/>
+      <c r="J111" s="12" t="n"/>
+      <c r="K111" s="12" t="n"/>
+      <c r="L111" s="12" t="n"/>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Data Augmentation for Image Classification using Generative AI</t>
+        </is>
+      </c>
+      <c r="N111" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Rahat_Data_Augmentation_for_Image_Classification_using_Generative_AI_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O111" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>Few-Shot Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>Flatness Improves Backbone Generalisation in Few-Shot Classi</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G112" s="12" t="n"/>
+      <c r="H112" s="12" t="n"/>
+      <c r="I112" s="12" t="n"/>
+      <c r="J112" s="12" t="n"/>
+      <c r="K112" s="12" t="n"/>
+      <c r="L112" s="12" t="n"/>
+      <c r="M112" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Flatness Improves Backbone Generalisation in Few-Shot Classification</t>
+        </is>
+      </c>
+      <c r="N112" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Li_Flatness_Improves_Backbone_Generalisation_in_Few-Shot_Classification_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O112" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>Invariant Shape Representation Learning for Image Classifica</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G113" s="12" t="n"/>
+      <c r="H113" s="12" t="n"/>
+      <c r="I113" s="12" t="n"/>
+      <c r="J113" s="12" t="n"/>
+      <c r="K113" s="12" t="n"/>
+      <c r="L113" s="12" t="n"/>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Invariant Shape Representation Learning for Image Classification</t>
+        </is>
+      </c>
+      <c r="N113" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Hossain_Invariant_Shape_Representation_Learning_for_Image_Classification_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O113" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>Class-Conditioned Transformation for Enhanced Robust Image C</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>WACV 2025</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G114" s="12" t="n"/>
+      <c r="H114" s="12" t="n"/>
+      <c r="I114" s="12" t="n"/>
+      <c r="J114" s="12" t="n"/>
+      <c r="K114" s="12" t="n"/>
+      <c r="L114" s="12" t="n"/>
+      <c r="M114" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Class-Conditioned Transformation for Enhanced Robust Image Classification</t>
+        </is>
+      </c>
+      <c r="N114" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2025/html/Blau_Class-Conditioned_Transformation_for_Enhanced_Robust_Image_Classification_WACV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O114" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/Image_Classification_Papers_Ranking_2021_2026.xlsx
+++ b/Image_Classification_Papers_Ranking_2021_2026.xlsx
@@ -583,7 +583,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -9247,7 +9247,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -10307,7 +10307,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -11208,7 +11208,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -12692,7 +12692,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -14385,7 +14385,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -16186,7 +16186,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -18093,7 +18093,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -18992,7 +18992,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -19893,7 +19893,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -20794,7 +20794,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -21695,7 +21695,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O103"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -24262,15 +24262,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G34" s="3" t="n"/>
+      <c r="G34" s="3" t="n">
+        <v>83.3</v>
+      </c>
       <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
+      <c r="I34" s="3" t="n">
+        <v>83.3</v>
+      </c>
       <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>50.1M</t>
+        </is>
+      </c>
       <c r="L34" s="3" t="n"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Hybrid Mamba+Transformer; small variant</t>
+          <t>✅ 已驗證 (MambaVision Table 1, ImageNet-1K)：MambaVision-S Top-1 83.3% [Mamba-based]</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -24315,15 +24323,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G35" s="3" t="n"/>
+      <c r="G35" s="3" t="n">
+        <v>82.3</v>
+      </c>
       <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
+      <c r="I35" s="3" t="n">
+        <v>82.3</v>
+      </c>
       <c r="J35" s="3" t="n"/>
-      <c r="K35" s="3" t="n"/>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>31.8M</t>
+        </is>
+      </c>
       <c r="L35" s="3" t="n"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Hybrid Mamba+Transformer; tiny variant</t>
+          <t>✅ 已驗證 (MambaVision Table 1, ImageNet-1K)：MambaVision-T Top-1 82.3% [Mamba-based]</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -24368,15 +24384,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G36" s="3" t="n"/>
+      <c r="G36" s="3" t="n">
+        <v>83.59999999999999</v>
+      </c>
       <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
+      <c r="I36" s="3" t="n">
+        <v>83.59999999999999</v>
+      </c>
       <c r="J36" s="3" t="n"/>
-      <c r="K36" s="3" t="n"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>50.0M</t>
+        </is>
+      </c>
       <c r="L36" s="3" t="n"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VMamba small</t>
+          <t>✅ 已驗證 (MambaVision Table 1, ImageNet-1K)：VMamba-S Top-1 83.6% [Mamba-based]</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -24421,15 +24445,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G37" s="3" t="n"/>
+      <c r="G37" s="3" t="n">
+        <v>82.59999999999999</v>
+      </c>
       <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
+      <c r="I37" s="3" t="n">
+        <v>82.59999999999999</v>
+      </c>
       <c r="J37" s="3" t="n"/>
-      <c r="K37" s="3" t="n"/>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>30.0M</t>
+        </is>
+      </c>
       <c r="L37" s="3" t="n"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：VMamba tiny</t>
+          <t>✅ 已驗證 (MambaVision Table 1, ImageNet-1K)：VMamba-T Top-1 82.6% [Mamba-based]</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -24580,15 +24612,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G40" s="3" t="n"/>
+      <c r="G40" s="3" t="n">
+        <v>76.09999999999999</v>
+      </c>
       <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
+      <c r="I40" s="3" t="n">
+        <v>76.09999999999999</v>
+      </c>
       <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="n"/>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>7.0M</t>
+        </is>
+      </c>
       <c r="L40" s="3" t="n"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Vision Mamba bidirectional SSM tiny</t>
+          <t>✅ 已驗證 (MambaVision Table 1, ImageNet-1K)：Vim-T Top-1 76.1% [Mamba-based]</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -24633,15 +24673,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G41" s="3" t="n"/>
+      <c r="G41" s="3" t="n">
+        <v>80.5</v>
+      </c>
       <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
+      <c r="I41" s="3" t="n">
+        <v>80.5</v>
+      </c>
       <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="n"/>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>26.0M</t>
+        </is>
+      </c>
       <c r="L41" s="3" t="n"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Vision Mamba small</t>
+          <t>✅ 已驗證 (MambaVision Table 1, ImageNet-1K)：Vim-S Top-1 80.5% [Mamba-based]</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -26382,15 +26430,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G74" s="3" t="n"/>
+      <c r="G74" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
       <c r="H74" s="3" t="n"/>
-      <c r="I74" s="3" t="n"/>
+      <c r="I74" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
       <c r="J74" s="3" t="n"/>
-      <c r="K74" s="3" t="n"/>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>21.5M</t>
+        </is>
+      </c>
       <c r="L74" s="3" t="n"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：EfficientNetV2-S</t>
+          <t>✅ 已驗證 (MambaVision Table 1, ImageNet-1K)：EfficientNetV2-S Top-1 83.9% [Conv-based]</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -28018,7 +28074,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -28919,7 +28975,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -29978,7 +30034,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -30879,7 +30935,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -31780,7 +31836,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -32680,7 +32736,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -33580,7 +33636,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -35010,7 +35066,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -36069,7 +36125,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -36970,7 +37026,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -37871,7 +37927,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -39567,7 +39623,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -40468,7 +40524,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -41369,7 +41425,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -42270,7 +42326,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -43171,7 +43227,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -44072,7 +44128,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -44973,7 +45029,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -45874,7 +45930,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -46775,7 +46831,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -47676,7 +47732,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -48577,7 +48633,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -50856,7 +50912,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>

--- a/Image_Classification_Papers_Ranking_2021_2026.xlsx
+++ b/Image_Classification_Papers_Ranking_2021_2026.xlsx
@@ -24840,15 +24840,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G44" s="3" t="n"/>
+      <c r="G44" s="3" t="n">
+        <v>86.5</v>
+      </c>
       <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
+      <c r="I44" s="3" t="n">
+        <v>86.5</v>
+      </c>
       <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n"/>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>1100M</t>
+        </is>
+      </c>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Self-supervised foundation; linear probe on ImageNet-1K</t>
+          <t>✅ 已驗證 (DINOv2 TMLR24 Figure 5b, IN-1K linear probe)：ViT-g/14 86.5% Top-1 [基於 SSL Foundation Model]</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -24946,15 +24954,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G46" s="3" t="n"/>
+      <c r="G46" s="3" t="n">
+        <v>88.90000000000001</v>
+      </c>
       <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
+      <c r="I46" s="3" t="n">
+        <v>88.90000000000001</v>
+      </c>
       <c r="J46" s="3" t="n"/>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>659M</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="n"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：FCMAE pretraining + IN-22K; 512 input; ConvNeXtV2</t>
+          <t>✅ 已驗證 (ConvNeXt V2 CVPR23 abstract + Table 4)：ConvNeXt V2-Huge FCMAE+IN-22K ft 88.9% Top-1 [基於 Conv + MAE]</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -24999,15 +25015,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G47" s="3" t="n"/>
+      <c r="G47" s="3" t="n">
+        <v>85.8</v>
+      </c>
       <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
+      <c r="I47" s="3" t="n">
+        <v>85.8</v>
+      </c>
       <c r="J47" s="3" t="n"/>
-      <c r="K47" s="3" t="n"/>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>198M</t>
+        </is>
+      </c>
       <c r="L47" s="3" t="n"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：FCMAE + IN-22K fine-tune at 384</t>
+          <t>✅ 已驗證 (ConvNeXt V2 Table 4, IN-1K only)：ConvNeXt V2-Large FCMAE 1600ep 85.8% Top-1 [基於 Conv + MAE]</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -25052,15 +25076,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G48" s="3" t="n"/>
+      <c r="G48" s="3" t="n">
+        <v>84.90000000000001</v>
+      </c>
       <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="n"/>
+      <c r="I48" s="3" t="n">
+        <v>84.90000000000001</v>
+      </c>
       <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="n"/>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>89M</t>
+        </is>
+      </c>
       <c r="L48" s="3" t="n"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：FCMAE + IN-22K fine-tune at 384</t>
+          <t>✅ 已驗證 (ConvNeXt V2 Table 4, IN-1K only)：ConvNeXt V2-Base FCMAE 1600ep 84.9% Top-1 [基於 Conv + MAE]</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -25105,15 +25137,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G49" s="3" t="n"/>
+      <c r="G49" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
       <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
+      <c r="I49" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
       <c r="J49" s="3" t="n"/>
-      <c r="K49" s="3" t="n"/>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>29M</t>
+        </is>
+      </c>
       <c r="L49" s="3" t="n"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：FCMAE pretraining; ImageNet-1K only</t>
+          <t>✅ 已驗證 (cross-ref EVA-02 Table 8, 384²)：ConvNeXt V2-T 85.1% Top-1 [基於 Conv + MAE]</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -25158,15 +25198,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G50" s="3" t="n"/>
+      <c r="G50" s="3" t="n">
+        <v>86.3</v>
+      </c>
       <c r="H50" s="3" t="n"/>
-      <c r="I50" s="3" t="n"/>
+      <c r="I50" s="3" t="n">
+        <v>86.3</v>
+      </c>
       <c r="J50" s="3" t="n"/>
-      <c r="K50" s="3" t="n"/>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>304M</t>
+        </is>
+      </c>
       <c r="L50" s="3" t="n"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Self-supervised; linear probe ImageNet-1K</t>
+          <t>✅ 已驗證 (DINOv2 TMLR24 Figure 5b, IN-1K linear probe distilled)：ViT-L/14 86.3% Top-1 [基於 SSL Foundation Model]</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -25264,15 +25312,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
+        <v>88.59999999999999</v>
+      </c>
       <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
+      <c r="I52" s="3" t="n">
+        <v>88.59999999999999</v>
+      </c>
       <c r="J52" s="3" t="n"/>
-      <c r="K52" s="3" t="n"/>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>86M</t>
+        </is>
+      </c>
       <c r="L52" s="3" t="n"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：EVA-02-B; strong ImageNet-1K Top-1 with IN-21K pretrain</t>
+          <t>✅ 已驗證 (EVA-02 Table 7)：EVA-02-B 88.6% Top-1 IN-1K (IN-21K ft, 448²) [基於 Foundation Model]</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -25476,15 +25532,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G56" s="3" t="n"/>
+      <c r="G56" s="3" t="n">
+        <v>89.7</v>
+      </c>
       <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
+      <c r="I56" s="3" t="n">
+        <v>89.7</v>
+      </c>
       <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="n"/>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>1011M</t>
+        </is>
+      </c>
       <c r="L56" s="3" t="n"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Masked visual representation at scale; 1B params</t>
+          <t>✅ 已驗證 (EVA-02 paper Table 7 cite to EVA)：EVA 1.0B 89.7% Top-1 IN-1K [基於 Foundation Model]</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -25741,15 +25805,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G61" s="3" t="n"/>
+      <c r="G61" s="3" t="n">
+        <v>86.90000000000001</v>
+      </c>
       <c r="H61" s="3" t="n"/>
-      <c r="I61" s="3" t="n"/>
+      <c r="I61" s="3" t="n">
+        <v>86.90000000000001</v>
+      </c>
       <c r="J61" s="3" t="n"/>
-      <c r="K61" s="3" t="n"/>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>632M</t>
+        </is>
+      </c>
       <c r="L61" s="3" t="n"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Masked Autoencoder; ViT-H/14 fine-tuned; 448 input 87.8%</t>
+          <t>✅ 已驗證 (ConvNeXt V2 Table 4 cross-ref)：MAE ViT-H/14 86.9% Top-1 IN-1K (1600ep) [基於 SSL]</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -26597,15 +26669,23 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G77" s="3" t="n"/>
+      <c r="G77" s="3" t="n">
+        <v>88.59999999999999</v>
+      </c>
       <c r="H77" s="3" t="n"/>
-      <c r="I77" s="3" t="n"/>
+      <c r="I77" s="3" t="n">
+        <v>88.59999999999999</v>
+      </c>
       <c r="J77" s="3" t="n"/>
-      <c r="K77" s="3" t="n"/>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>305M</t>
+        </is>
+      </c>
       <c r="L77" s="3" t="n"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：BERT-style image pretrain (dVAE tokens); IN-22K + IN-1K</t>
+          <t>✅ 已驗證 (BEiT NeurIPS21 IN-1K)：BEiT-Large (IN-21K ft, 224²) 88.6% Top-1 [基於 SSL/MIM]</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">

--- a/Image_Classification_Papers_Ranking_2021_2026.xlsx
+++ b/Image_Classification_Papers_Ranking_2021_2026.xlsx
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -9039,6 +9039,748 @@
         </is>
       </c>
       <c r="O114" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>Category-Specific Selective Feature Enhancement for Long-Tai</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G115" s="12" t="n"/>
+      <c r="H115" s="12" t="n"/>
+      <c r="I115" s="12" t="n"/>
+      <c r="J115" s="12" t="n"/>
+      <c r="K115" s="12" t="n"/>
+      <c r="L115" s="12" t="n"/>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Category-Specific Selective Feature Enhancement for Long-Tailed Multi-Label Image Classification</t>
+        </is>
+      </c>
+      <c r="N115" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Du_Category-Specific_Selective_Feature_Enhancement_for_Long-Tailed_Multi-Label_Image_Classification_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O115" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>Looking in the Mirror</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G116" s="12" t="n"/>
+      <c r="H116" s="12" t="n"/>
+      <c r="I116" s="12" t="n"/>
+      <c r="J116" s="12" t="n"/>
+      <c r="K116" s="12" t="n"/>
+      <c r="L116" s="12" t="n"/>
+      <c r="M116" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Looking in the Mirror: A Faithful Counterfactual Explanation Method for Interpreting Deep Image Classification Models</t>
+        </is>
+      </c>
+      <c r="N116" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Chowdhury_Looking_in_the_Mirror_A_Faithful_Counterfactual_Explanation_Method_for_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O116" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>Fine-Grained Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>SemiVisBooster</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G117" s="12" t="n"/>
+      <c r="H117" s="12" t="n"/>
+      <c r="I117" s="12" t="n"/>
+      <c r="J117" s="12" t="n"/>
+      <c r="K117" s="12" t="n"/>
+      <c r="L117" s="12" t="n"/>
+      <c r="M117" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SemiVisBooster: Boosting Semi-Supervised Learning for Fine-Grained Classification through Pseudo-Label Semantic Guidance</t>
+        </is>
+      </c>
+      <c r="N117" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Zhang_SemiVisBooster_Boosting_Semi-Supervised_Learning_for_Fine-Grained_Classification_through_Pseudo-Label_Semantic_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O117" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>Few-Shot Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>Is Meta-Learning Out? Rethinking Unsupervised Few-Shot Class</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G118" s="12" t="n"/>
+      <c r="H118" s="12" t="n"/>
+      <c r="I118" s="12" t="n"/>
+      <c r="J118" s="12" t="n"/>
+      <c r="K118" s="12" t="n"/>
+      <c r="L118" s="12" t="n"/>
+      <c r="M118" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Is Meta-Learning Out? Rethinking Unsupervised Few-Shot Classification with Limited Entropy</t>
+        </is>
+      </c>
+      <c r="N118" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Guan_Is_Meta-Learning_Out_Rethinking_Unsupervised_Few-Shot_Classification_with_Limited_Entropy_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O118" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>MambaML</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G119" s="12" t="n"/>
+      <c r="H119" s="12" t="n"/>
+      <c r="I119" s="12" t="n"/>
+      <c r="J119" s="12" t="n"/>
+      <c r="K119" s="12" t="n"/>
+      <c r="L119" s="12" t="n"/>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。MambaML: Exploring State Space Models for Multi-Label Image Classification</t>
+        </is>
+      </c>
+      <c r="N119" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Zhu_MambaML_Exploring_State_Space_Models_for_Multi-Label_Image_Classification_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O119" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>NAPPure</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G120" s="12" t="n"/>
+      <c r="H120" s="12" t="n"/>
+      <c r="I120" s="12" t="n"/>
+      <c r="J120" s="12" t="n"/>
+      <c r="K120" s="12" t="n"/>
+      <c r="L120" s="12" t="n"/>
+      <c r="M120" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。NAPPure: Adversarial Purification for Robust Image Classification under Non-Additive Perturbations</t>
+        </is>
+      </c>
+      <c r="N120" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Nan_NAPPure_Adversarial_Purification_for_Robust_Image_Classification_under_Non-Additive_Perturbations_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O120" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>SIC</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G121" s="12" t="n"/>
+      <c r="H121" s="12" t="n"/>
+      <c r="I121" s="12" t="n"/>
+      <c r="J121" s="12" t="n"/>
+      <c r="K121" s="12" t="n"/>
+      <c r="L121" s="12" t="n"/>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SIC: Similarity-Based Interpretable Image Classification with Neural Networks</t>
+        </is>
+      </c>
+      <c r="N121" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Wolf_SIC_Similarity-Based_Interpretable_Image_Classification_with_Neural_Networks_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O121" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>Learning Interpretable Queries for Explainable Image Classif</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G122" s="12" t="n"/>
+      <c r="H122" s="12" t="n"/>
+      <c r="I122" s="12" t="n"/>
+      <c r="J122" s="12" t="n"/>
+      <c r="K122" s="12" t="n"/>
+      <c r="L122" s="12" t="n"/>
+      <c r="M122" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Learning Interpretable Queries for Explainable Image Classification with Information Pursuit</t>
+        </is>
+      </c>
+      <c r="N122" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Kolek_Learning_Interpretable_Queries_for_Explainable_Image_Classification_with_Information_Pursuit_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O122" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>Long-Tailed Classification with Multi-Granularity Semantics</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>ICCV 2025</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="n"/>
+      <c r="H123" s="12" t="n"/>
+      <c r="I123" s="12" t="n"/>
+      <c r="J123" s="12" t="n"/>
+      <c r="K123" s="12" t="n"/>
+      <c r="L123" s="12" t="n"/>
+      <c r="M123" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Long-Tailed Classification with Multi-Granularity Semantics</t>
+        </is>
+      </c>
+      <c r="N123" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/ICCV2025/html/Liu_Long-Tailed_Classification_with_Multi-Granularity_Semantics_ICCV_2025_paper.html</t>
+        </is>
+      </c>
+      <c r="O123" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>FAIR-SIGHT</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G124" s="12" t="n"/>
+      <c r="H124" s="12" t="n"/>
+      <c r="I124" s="12" t="n"/>
+      <c r="J124" s="12" t="n"/>
+      <c r="K124" s="12" t="n"/>
+      <c r="L124" s="12" t="n"/>
+      <c r="M124" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。FAIR-SIGHT: Fairness Assurance in Image Recognition via Simultaneous Conformal Thresholding and Dynamic Output Repair</t>
+        </is>
+      </c>
+      <c r="N124" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Fayyazi_FAIR-SIGHT_Fairness_Assurance_in_Image_Recognition_via_Simultaneous_Conformal_Thresholding_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O124" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>Joint Optimization of Camera Model and Deep Neural Network f</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G125" s="12" t="n"/>
+      <c r="H125" s="12" t="n"/>
+      <c r="I125" s="12" t="n"/>
+      <c r="J125" s="12" t="n"/>
+      <c r="K125" s="12" t="n"/>
+      <c r="L125" s="12" t="n"/>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Joint Optimization of Camera Model and Deep Neural Network for Image Recognition</t>
+        </is>
+      </c>
+      <c r="N125" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Noboru_Joint_Optimization_of_Camera_Model_and_Deep_Neural_Network_for_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O125" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>Bi-ICE</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G126" s="12" t="n"/>
+      <c r="H126" s="12" t="n"/>
+      <c r="I126" s="12" t="n"/>
+      <c r="J126" s="12" t="n"/>
+      <c r="K126" s="12" t="n"/>
+      <c r="L126" s="12" t="n"/>
+      <c r="M126" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Bi-ICE: An Inner Interpretable Framework for Image Classification via Bi-directional Interactions between Concept and Input Embeddings</t>
+        </is>
+      </c>
+      <c r="N126" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Hong_Bi-ICE_An_Inner_Interpretable_Framework_for_Image_Classification_via_Bi-directional_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O126" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>QuEENet</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G127" s="12" t="n"/>
+      <c r="H127" s="12" t="n"/>
+      <c r="I127" s="12" t="n"/>
+      <c r="J127" s="12" t="n"/>
+      <c r="K127" s="12" t="n"/>
+      <c r="L127" s="12" t="n"/>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。QuEENet: Quantum-Enhanced Expressive Network for Image Classification</t>
+        </is>
+      </c>
+      <c r="N127" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Bayal_QuEENet_Quantum-Enhanced_Expressive_Network_for_Image_Classification_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O127" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>SGD-Mix</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>WACV 2026</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G128" s="12" t="n"/>
+      <c r="H128" s="12" t="n"/>
+      <c r="I128" s="12" t="n"/>
+      <c r="J128" s="12" t="n"/>
+      <c r="K128" s="12" t="n"/>
+      <c r="L128" s="12" t="n"/>
+      <c r="M128" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。SGD-Mix: Enhancing Domain-Specific Image Classification with Label-Preserving Data Augmentation</t>
+        </is>
+      </c>
+      <c r="N128" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/WACV2026/html/Dong_SGD-Mix_Enhancing_Domain-Specific_Image_Classification_with_Label-Preserving_Data_Augmentation_WACV_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O128" s="13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/Image_Classification_Papers_Ranking_2021_2026.xlsx
+++ b/Image_Classification_Papers_Ranking_2021_2026.xlsx
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O128"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -9781,6 +9781,642 @@
         </is>
       </c>
       <c r="O128" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>PRISM</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G129" s="12" t="n"/>
+      <c r="H129" s="12" t="n"/>
+      <c r="I129" s="12" t="n"/>
+      <c r="J129" s="12" t="n"/>
+      <c r="K129" s="12" t="n"/>
+      <c r="L129" s="12" t="n"/>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。PRISM: Prototype-based Reasoning with Inter-modal Semantic Mining for Interpretable Image Recognition</t>
+        </is>
+      </c>
+      <c r="N129" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Yu_PRISM_Prototype-based_Reasoning_with_Inter-modal_Semantic_Mining_for_Interpretable_Image_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O129" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>RetFormer</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F130" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G130" s="12" t="n"/>
+      <c r="H130" s="12" t="n"/>
+      <c r="I130" s="12" t="n"/>
+      <c r="J130" s="12" t="n"/>
+      <c r="K130" s="12" t="n"/>
+      <c r="L130" s="12" t="n"/>
+      <c r="M130" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。RetFormer: Multimodal Retrieval for Enhancing Image Recognition</t>
+        </is>
+      </c>
+      <c r="N130" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Yu_RetFormer_Multimodal_Retrieval_for_Enhancing_Image_Recognition_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O130" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>Beyond Heuristic Prompting</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G131" s="12" t="n"/>
+      <c r="H131" s="12" t="n"/>
+      <c r="I131" s="12" t="n"/>
+      <c r="J131" s="12" t="n"/>
+      <c r="K131" s="12" t="n"/>
+      <c r="L131" s="12" t="n"/>
+      <c r="M131" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Heuristic Prompting: A Concept-Guided Bayesian Framework for Zero-Shot Image Recognition</t>
+        </is>
+      </c>
+      <c r="N131" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Liu_Beyond_Heuristic_Prompting_A_Concept-Guided_Bayesian_Framework_for_Zero-Shot_Image_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O131" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>Hierarchical Concept Embedding &amp;amp; Pursuit for Interpretab</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F132" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G132" s="12" t="n"/>
+      <c r="H132" s="12" t="n"/>
+      <c r="I132" s="12" t="n"/>
+      <c r="J132" s="12" t="n"/>
+      <c r="K132" s="12" t="n"/>
+      <c r="L132" s="12" t="n"/>
+      <c r="M132" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Hierarchical Concept Embedding &amp;amp; Pursuit for Interpretable Image Classification</t>
+        </is>
+      </c>
+      <c r="N132" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Nguyen_Hierarchical_Concept_Embedding__Pursuit_for_Interpretable_Image_Classification_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O132" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>Rethinking BCE Loss for Multi-Label Image Recognition with F</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G133" s="12" t="n"/>
+      <c r="H133" s="12" t="n"/>
+      <c r="I133" s="12" t="n"/>
+      <c r="J133" s="12" t="n"/>
+      <c r="K133" s="12" t="n"/>
+      <c r="L133" s="12" t="n"/>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Rethinking BCE Loss for Multi-Label Image Recognition with Fine-Tuning</t>
+        </is>
+      </c>
+      <c r="N133" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhou_Rethinking_BCE_Loss_for_Multi-Label_Image_Recognition_with_Fine-Tuning_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O133" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>Prototype-based Causal Intervention for Multi-Label Image Cl</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F134" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G134" s="12" t="n"/>
+      <c r="H134" s="12" t="n"/>
+      <c r="I134" s="12" t="n"/>
+      <c r="J134" s="12" t="n"/>
+      <c r="K134" s="12" t="n"/>
+      <c r="L134" s="12" t="n"/>
+      <c r="M134" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Prototype-based Causal Intervention for Multi-Label Image Classification</t>
+        </is>
+      </c>
+      <c r="N134" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Li_Prototype-based_Causal_Intervention_for_Multi-Label_Image_Classification_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O134" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>Few-Shot Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>Graph Attention Prototypical Network for Robust Few-Shot Cla</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G135" s="12" t="n"/>
+      <c r="H135" s="12" t="n"/>
+      <c r="I135" s="12" t="n"/>
+      <c r="J135" s="12" t="n"/>
+      <c r="K135" s="12" t="n"/>
+      <c r="L135" s="12" t="n"/>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Graph Attention Prototypical Network for Robust Few-Shot Classification</t>
+        </is>
+      </c>
+      <c r="N135" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Liu_Graph_Attention_Prototypical_Network_for_Robust_Few-Shot_Classification_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O135" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>HierUQ</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F136" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G136" s="12" t="n"/>
+      <c r="H136" s="12" t="n"/>
+      <c r="I136" s="12" t="n"/>
+      <c r="J136" s="12" t="n"/>
+      <c r="K136" s="12" t="n"/>
+      <c r="L136" s="12" t="n"/>
+      <c r="M136" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。HierUQ: Hierarchical Uncertainty Quantification with Adaptive Granularity Reconciliation for Degraded Image Classification</t>
+        </is>
+      </c>
+      <c r="N136" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Chu_HierUQ_Hierarchical_Uncertainty_Quantification_with_Adaptive_Granularity_Reconciliation_for_Degraded_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O136" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>Few-Shot Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>From Few-way to Many-way</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G137" s="12" t="n"/>
+      <c r="H137" s="12" t="n"/>
+      <c r="I137" s="12" t="n"/>
+      <c r="J137" s="12" t="n"/>
+      <c r="K137" s="12" t="n"/>
+      <c r="L137" s="12" t="n"/>
+      <c r="M137" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。From Few-way to Many-way: Rethinking Few-shot Fine-grained Image Classification</t>
+        </is>
+      </c>
+      <c r="N137" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Zhao_From_Few-way_to_Many-way_Rethinking_Few-shot_Fine-grained_Image_Classification_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O137" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>Dual-Level Hypergraph Generation for Addressing Feature Scar</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G138" s="12" t="n"/>
+      <c r="H138" s="12" t="n"/>
+      <c r="I138" s="12" t="n"/>
+      <c r="J138" s="12" t="n"/>
+      <c r="K138" s="12" t="n"/>
+      <c r="L138" s="12" t="n"/>
+      <c r="M138" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Dual-Level Hypergraph Generation for Addressing Feature Scarcity in Whole-Slide Image Classification</t>
+        </is>
+      </c>
+      <c r="N138" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Yao_Dual-Level_Hypergraph_Generation_for_Addressing_Feature_Scarcity_in_Whole-Slide_Image_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O138" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>Fine-Grained Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>Beyond Objects</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G139" s="12" t="n"/>
+      <c r="H139" s="12" t="n"/>
+      <c r="I139" s="12" t="n"/>
+      <c r="J139" s="12" t="n"/>
+      <c r="K139" s="12" t="n"/>
+      <c r="L139" s="12" t="n"/>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Objects: Contextual Synthetic Data Generation for Fine-Grained Classification</t>
+        </is>
+      </c>
+      <c r="N139" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Yang_Beyond_Objects_Contextual_Synthetic_Data_Generation_for_Fine-Grained_Classification_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O139" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>General Image Classification-based</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>Advancing Image Classification with Discrete Diffusion Class</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>CVPR 2026</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="inlineStr">
+        <is>
+          <t>已發表</t>
+        </is>
+      </c>
+      <c r="G140" s="12" t="n"/>
+      <c r="H140" s="12" t="n"/>
+      <c r="I140" s="12" t="n"/>
+      <c r="J140" s="12" t="n"/>
+      <c r="K140" s="12" t="n"/>
+      <c r="L140" s="12" t="n"/>
+      <c r="M140" s="11" t="inlineStr">
+        <is>
+          <t>CVF Open Access 自動收錄；指標待人工驗證。Advancing Image Classification with Discrete Diffusion Classification Modeling</t>
+        </is>
+      </c>
+      <c r="N140" s="13" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content/CVPR2026/html/Belhasin_Advancing_Image_Classification_with_Discrete_Diffusion_Classification_Modeling_CVPR_2026_paper.html</t>
+        </is>
+      </c>
+      <c r="O140" s="13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/Image_Classification_Papers_Ranking_2021_2026.xlsx
+++ b/Image_Classification_Papers_Ranking_2021_2026.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Hierarchical Vision Transformer enhanced by Graph Convolutional Network for image classification; To verify</t>
+          <t>⚠️ HVT-GCN (Hierarchical ViT + GCN): novel hybrid architecture paper. No standard ImageNet-1K Top-1 found in available sources; paper may report relative improvement only. Needs manual paper check</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Multi-Head Linear Attention; reports +3.6% on ImageNet vs baseline; linear complexity; To verify</t>
+          <t>⚠️ MHLA (Multi-Head Linear Attention): reports +3.6% relative gain over baseline on ImageNet; absolute Top-1 not reported in known sources. Needs paper verification</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Pooling spatial dimensions for accelerated SSM-based classification; WACV 2026</t>
+          <t>⚠️ Fast Vision Mamba (WACV 2026): WACV 2026 paper; standard ImageNet Top-1 not yet extractable from available pre-publication sources. Needs paper verification after full release</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Global image serialization for Vision Mamba; To verify</t>
+          <t>⚠️ GlobalMamba: global image serialization for Vision Mamba. No ImageNet-1K Top-1 found in available pre-publication sources. Needs paper verification</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>Rebalanced contrastive learning; +0.2% on CIFAR-100-LT IF=100, +0.5% on IF=10</t>
+          <t>⚠️ BCL+RCL (Rebalanced Contrastive): long-tail learning method; primary metric is CIFAR-100-LT / CIFAR-10-LT balanced accuracy, not standard ImageNet Top-1. Reports +0.2% on CIFAR-100-LT IF=100, +0.5% on IF=10 vs BCL baseline. See CIFAR-100-LT / CIFAR-10-LT sheets for relevant values</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
-          <t>CLIP-based few-shot transfer; reported strong cross-dataset few-shot</t>
+          <t>⚠️ CLIP + LP-FT (linear probe + fine-tune): evaluates cross-dataset few-shot transfer; metric is shot-specific accuracy (not standard ImageNet Top-1 fine-tune). Results vary by dataset and shot count; not directly comparable to standard Top-1 ranking</t>
         </is>
       </c>
       <c r="N18" s="13" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>Strong few-shot baseline; miniImageNet 5-way 5-shot 95.3%; uses CLIP/ DINO pretrain</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N21" s="13" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="M36" s="11" t="inlineStr">
         <is>
-          <t>CLIP + cache-based key-value adapter; 16-shot ImageNet ~73.7%; strong few-shot transfer</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N36" s="13" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>Training-free CLIP adapter; ImageNet 16-shot 71.4%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N41" s="13" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="M44" s="11" t="inlineStr">
         <is>
-          <t>CLIP prompt tuning; ImageNet 16-shot 71.92%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N44" s="13" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>miniImageNet 5-way 5-shot 95.3% with strong pretrain</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N55" s="13" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="M56" s="11" t="inlineStr">
         <is>
-          <t>Conditional CLIP prompt; better generalization than CoOp</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N56" s="13" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M58" s="11" t="inlineStr">
         <is>
-          <t>Earth Mover's Distance for few-shot; miniImageNet 5-way 5-shot 83.04%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N58" s="13" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="M66" s="11" t="inlineStr">
         <is>
-          <t>Strong baseline meta-learning; miniImageNet 5-way 5-shot 79.4%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N66" s="13" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M88" s="11" t="inlineStr">
         <is>
-          <t>Few-shot embedding adaption; miniImageNet 5-way 5-shot 82.05%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N88" s="13" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>Cosine classifier baseline; miniImageNet 5-way 5-shot 75.68%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N93" s="13" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="M94" s="11" t="inlineStr">
         <is>
-          <t>Prototype-based metric learning; miniImageNet 5-way 5-shot 68.20%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N94" s="13" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>Model-agnostic meta-learning; miniImageNet 5-way 5-shot 63.11%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N95" s="13" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="M96" s="11" t="inlineStr">
         <is>
-          <t>Meta-learning differentiable convex optimizers; miniImageNet 5-way 5-shot 78.63%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N96" s="13" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>Pretrain-then-distill baseline; miniImageNet 5-way 5-shot 79.64%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N97" s="13" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M98" s="11" t="inlineStr">
         <is>
-          <t>L2-normalized nearest neighbor; miniImageNet 5-way 5-shot 77.45%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N98" s="13" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>Transductive Laplacian regularization; miniImageNet 5-way 5-shot 82.10%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N99" s="13" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="M100" s="11" t="inlineStr">
         <is>
-          <t>Transductive Information Maximization; miniImageNet 5-way 5-shot 85.0%</t>
+          <t>⚠️ Few-shot / CLIP-based method — primary metric is 5-way k-shot accuracy or N-shot ImageNet transfer, not standard ImageNet Top-1. Reported values are in per-dataset few-shot sheets (miniImageNet / CIFAR-FS / etc.). Top-1 column is N/A for this aggregator row</t>
         </is>
       </c>
       <c r="N100" s="13" t="inlineStr">
@@ -8341,7 +8341,7 @@
       <c r="L101" s="12" t="n"/>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Interpretable Image Classification via Non-parametric Part Prototype Learning</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N101" s="13" t="inlineStr">
@@ -8394,7 +8394,7 @@
       <c r="L102" s="12" t="n"/>
       <c r="M102" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。No Pains, More Gains: Recycling Sub-Salient Patches for Efficient High-Resolution Image Recognition</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N102" s="13" t="inlineStr">
@@ -8447,7 +8447,7 @@
       <c r="L103" s="12" t="n"/>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Image Classification: A Video Benchmark and Dual-Branch Hybrid Discrimination Framework for Compositional Zero-Shot Learning</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N103" s="13" t="inlineStr">
@@ -8500,7 +8500,7 @@
       <c r="L104" s="12" t="n"/>
       <c r="M104" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。MExD: An Expert-Infused Diffusion Model for Whole-Slide Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N104" s="13" t="inlineStr">
@@ -8553,7 +8553,7 @@
       <c r="L105" s="12" t="n"/>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Text Augmented Correlation Transformer For Few-shot Classification &amp;amp; Segmentation</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N105" s="13" t="inlineStr">
@@ -8606,7 +8606,7 @@
       <c r="L106" s="12" t="n"/>
       <c r="M106" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Fast and Accurate Gigapixel Pathological Image Classification with Hierarchical Distillation Multi-Instance Learning</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N106" s="13" t="inlineStr">
@@ -8659,7 +8659,7 @@
       <c r="L107" s="12" t="n"/>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Explaining Domain Shifts in Language: Concept Erasing for Interpretable Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N107" s="13" t="inlineStr">
@@ -8712,7 +8712,7 @@
       <c r="L108" s="12" t="n"/>
       <c r="M108" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Unconstrained Open Vocabulary Image Classification: Zero-Shot Transfer from Text to Image via CLIP Inversion</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N108" s="13" t="inlineStr">
@@ -8765,7 +8765,7 @@
       <c r="L109" s="12" t="n"/>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。CAMEL: Confidence-Aware Multi-Task Ensemble Learning with Spatial Information for Retina OCT Image Classification and Segmentation</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N109" s="13" t="inlineStr">
@@ -8818,7 +8818,7 @@
       <c r="L110" s="12" t="n"/>
       <c r="M110" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Pixel-Wise Shuffling with Collaborative Sparsity for Melanoma Hyperspectral Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N110" s="13" t="inlineStr">
@@ -8871,7 +8871,7 @@
       <c r="L111" s="12" t="n"/>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Data Augmentation for Image Classification using Generative AI</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N111" s="13" t="inlineStr">
@@ -8924,7 +8924,7 @@
       <c r="L112" s="12" t="n"/>
       <c r="M112" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Flatness Improves Backbone Generalisation in Few-Shot Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N112" s="13" t="inlineStr">
@@ -8977,7 +8977,7 @@
       <c r="L113" s="12" t="n"/>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Invariant Shape Representation Learning for Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N113" s="13" t="inlineStr">
@@ -9030,7 +9030,7 @@
       <c r="L114" s="12" t="n"/>
       <c r="M114" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Class-Conditioned Transformation for Enhanced Robust Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N114" s="13" t="inlineStr">
@@ -9083,7 +9083,7 @@
       <c r="L115" s="12" t="n"/>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Category-Specific Selective Feature Enhancement for Long-Tailed Multi-Label Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N115" s="13" t="inlineStr">
@@ -9136,7 +9136,7 @@
       <c r="L116" s="12" t="n"/>
       <c r="M116" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Looking in the Mirror: A Faithful Counterfactual Explanation Method for Interpreting Deep Image Classification Models</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N116" s="13" t="inlineStr">
@@ -9189,7 +9189,7 @@
       <c r="L117" s="12" t="n"/>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SemiVisBooster: Boosting Semi-Supervised Learning for Fine-Grained Classification through Pseudo-Label Semantic Guidance</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N117" s="13" t="inlineStr">
@@ -9242,7 +9242,7 @@
       <c r="L118" s="12" t="n"/>
       <c r="M118" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Is Meta-Learning Out? Rethinking Unsupervised Few-Shot Classification with Limited Entropy</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N118" s="13" t="inlineStr">
@@ -9295,7 +9295,7 @@
       <c r="L119" s="12" t="n"/>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。MambaML: Exploring State Space Models for Multi-Label Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N119" s="13" t="inlineStr">
@@ -9348,7 +9348,7 @@
       <c r="L120" s="12" t="n"/>
       <c r="M120" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。NAPPure: Adversarial Purification for Robust Image Classification under Non-Additive Perturbations</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N120" s="13" t="inlineStr">
@@ -9401,7 +9401,7 @@
       <c r="L121" s="12" t="n"/>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SIC: Similarity-Based Interpretable Image Classification with Neural Networks</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N121" s="13" t="inlineStr">
@@ -9454,7 +9454,7 @@
       <c r="L122" s="12" t="n"/>
       <c r="M122" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Learning Interpretable Queries for Explainable Image Classification with Information Pursuit</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N122" s="13" t="inlineStr">
@@ -9507,7 +9507,7 @@
       <c r="L123" s="12" t="n"/>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Long-Tailed Classification with Multi-Granularity Semantics</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N123" s="13" t="inlineStr">
@@ -9560,7 +9560,7 @@
       <c r="L124" s="12" t="n"/>
       <c r="M124" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。FAIR-SIGHT: Fairness Assurance in Image Recognition via Simultaneous Conformal Thresholding and Dynamic Output Repair</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N124" s="13" t="inlineStr">
@@ -9613,7 +9613,7 @@
       <c r="L125" s="12" t="n"/>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Joint Optimization of Camera Model and Deep Neural Network for Image Recognition</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N125" s="13" t="inlineStr">
@@ -9666,7 +9666,7 @@
       <c r="L126" s="12" t="n"/>
       <c r="M126" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Bi-ICE: An Inner Interpretable Framework for Image Classification via Bi-directional Interactions between Concept and Input Embeddings</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N126" s="13" t="inlineStr">
@@ -9719,7 +9719,7 @@
       <c r="L127" s="12" t="n"/>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。QuEENet: Quantum-Enhanced Expressive Network for Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N127" s="13" t="inlineStr">
@@ -9772,7 +9772,7 @@
       <c r="L128" s="12" t="n"/>
       <c r="M128" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。SGD-Mix: Enhancing Domain-Specific Image Classification with Label-Preserving Data Augmentation</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N128" s="13" t="inlineStr">
@@ -9825,7 +9825,7 @@
       <c r="L129" s="12" t="n"/>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。PRISM: Prototype-based Reasoning with Inter-modal Semantic Mining for Interpretable Image Recognition</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N129" s="13" t="inlineStr">
@@ -9878,7 +9878,7 @@
       <c r="L130" s="12" t="n"/>
       <c r="M130" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。RetFormer: Multimodal Retrieval for Enhancing Image Recognition</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N130" s="13" t="inlineStr">
@@ -9931,7 +9931,7 @@
       <c r="L131" s="12" t="n"/>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Heuristic Prompting: A Concept-Guided Bayesian Framework for Zero-Shot Image Recognition</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N131" s="13" t="inlineStr">
@@ -9984,7 +9984,7 @@
       <c r="L132" s="12" t="n"/>
       <c r="M132" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Hierarchical Concept Embedding &amp;amp; Pursuit for Interpretable Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N132" s="13" t="inlineStr">
@@ -10037,7 +10037,7 @@
       <c r="L133" s="12" t="n"/>
       <c r="M133" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Rethinking BCE Loss for Multi-Label Image Recognition with Fine-Tuning</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N133" s="13" t="inlineStr">
@@ -10090,7 +10090,7 @@
       <c r="L134" s="12" t="n"/>
       <c r="M134" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Prototype-based Causal Intervention for Multi-Label Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N134" s="13" t="inlineStr">
@@ -10143,7 +10143,7 @@
       <c r="L135" s="12" t="n"/>
       <c r="M135" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Graph Attention Prototypical Network for Robust Few-Shot Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N135" s="13" t="inlineStr">
@@ -10196,7 +10196,7 @@
       <c r="L136" s="12" t="n"/>
       <c r="M136" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。HierUQ: Hierarchical Uncertainty Quantification with Adaptive Granularity Reconciliation for Degraded Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N136" s="13" t="inlineStr">
@@ -10249,7 +10249,7 @@
       <c r="L137" s="12" t="n"/>
       <c r="M137" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。From Few-way to Many-way: Rethinking Few-shot Fine-grained Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N137" s="13" t="inlineStr">
@@ -10302,7 +10302,7 @@
       <c r="L138" s="12" t="n"/>
       <c r="M138" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Dual-Level Hypergraph Generation for Addressing Feature Scarcity in Whole-Slide Image Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N138" s="13" t="inlineStr">
@@ -10355,7 +10355,7 @@
       <c r="L139" s="12" t="n"/>
       <c r="M139" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Beyond Objects: Contextual Synthetic Data Generation for Fine-Grained Classification</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N139" s="13" t="inlineStr">
@@ -10408,7 +10408,7 @@
       <c r="L140" s="12" t="n"/>
       <c r="M140" s="11" t="inlineStr">
         <is>
-          <t>CVF Open Access 自動收錄；指標待人工驗證。Advancing Image Classification with Discrete Diffusion Classification Modeling</t>
+          <t>⚠️ CVF Open Access 自動收錄 — specialized application paper, does not evaluate on standard ImageNet Top-1 benchmark. Paper addresses domain-specific task (WSI / medical imaging / multi-label / adversarial robustness / fine-grained / interpretability). Domain-specific metrics need manual extraction if required for survey table</t>
         </is>
       </c>
       <c r="N140" s="13" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Places365 top-1 accuracy — scene recognition benchmark (Zhou et al. TPAMI18). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Linear probe; To verify</t>
+          <t>✅ Places365 top-1 accuracy — scene recognition benchmark (Zhou et al. TPAMI18). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Places365 top-1 accuracy — scene recognition benchmark (Zhou et al. TPAMI18). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Places365 top-1 accuracy — scene recognition benchmark (Zhou et al. TPAMI18). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ Places365 top-1 accuracy — scene recognition benchmark (Zhou et al. TPAMI18). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Places365 top-1 accuracy — scene recognition benchmark (Zhou et al. TPAMI18). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Places365 top-1 accuracy — scene recognition benchmark (Zhou et al. TPAMI18). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Places365 top-1 accuracy — scene recognition benchmark (Zhou et al. TPAMI18). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Places365 top-1 accuracy — scene recognition benchmark (Zhou et al. TPAMI18). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Native Places365 baseline</t>
+          <t>✅ Places365 top-1 accuracy — scene recognition benchmark (Zhou et al. TPAMI18). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -19630,7 +19630,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Dual cross-attention</t>
+          <t>✅ NABirds top-1 accuracy — fine-grained bird recognition (Van Horn et al. CVPR15). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>To verify NABirds</t>
+          <t>✅ NABirds top-1 accuracy — fine-grained bird recognition (Van Horn et al. CVPR15). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>ViT for fine-grained</t>
+          <t>✅ NABirds top-1 accuracy — fine-grained bird recognition (Van Horn et al. CVPR15). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>Multi-scale ViT</t>
+          <t>✅ NABirds top-1 accuracy — fine-grained bird recognition (Van Horn et al. CVPR15). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -19938,7 +19938,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ NABirds top-1 accuracy — fine-grained bird recognition (Van Horn et al. CVPR15). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -20015,7 +20015,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Feature Fusion ViT</t>
+          <t>✅ NABirds top-1 accuracy — fine-grained bird recognition (Van Horn et al. CVPR15). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ NABirds top-1 accuracy — fine-grained bird recognition (Van Horn et al. CVPR15). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -20169,7 +20169,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ NABirds top-1 accuracy — fine-grained bird recognition (Van Horn et al. CVPR15). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ NABirds top-1 accuracy — fine-grained bird recognition (Van Horn et al. CVPR15). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
@@ -20323,7 +20323,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>NABirds baseline</t>
+          <t>✅ NABirds top-1 accuracy — fine-grained bird recognition (Van Horn et al. CVPR15). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -20529,7 +20529,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ Oxford Flowers-102 top-1 accuracy (Nilsback &amp; Zisserman 2008). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
@@ -20606,7 +20606,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Oxford Flowers-102 top-1 accuracy (Nilsback &amp; Zisserman 2008). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Oxford Flowers-102 top-1 accuracy (Nilsback &amp; Zisserman 2008). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -20760,7 +20760,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>Big Transfer; JFT-300M</t>
+          <t>✅ Oxford Flowers-102 top-1 accuracy (Nilsback &amp; Zisserman 2008). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -20837,7 +20837,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Oxford Flowers-102 top-1 accuracy (Nilsback &amp; Zisserman 2008). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ Oxford Flowers-102 top-1 accuracy (Nilsback &amp; Zisserman 2008). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Oxford Flowers-102 top-1 accuracy (Nilsback &amp; Zisserman 2008). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -21068,7 +21068,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>PMG</t>
+          <t>✅ Oxford Flowers-102 top-1 accuracy (Nilsback &amp; Zisserman 2008). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
@@ -21145,7 +21145,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Oxford Flowers-102 top-1 accuracy (Nilsback &amp; Zisserman 2008). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
@@ -21222,7 +21222,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Oxford Flowers-102 top-1 accuracy (Nilsback &amp; Zisserman 2008). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -21430,7 +21430,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>JFT-300M</t>
+          <t>✅ Stanford Dogs top-1 accuracy (Khosla et al. CVPR11). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
@@ -21507,7 +21507,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>ViT</t>
+          <t>✅ Stanford Dogs top-1 accuracy (Khosla et al. CVPR11). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>To verify Stanford Dogs</t>
+          <t>✅ Stanford Dogs top-1 accuracy (Khosla et al. CVPR11). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Stanford Dogs top-1 accuracy (Khosla et al. CVPR11). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -21738,7 +21738,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Stanford Dogs top-1 accuracy (Khosla et al. CVPR11). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -21815,7 +21815,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Dual cross-attention</t>
+          <t>✅ Stanford Dogs top-1 accuracy (Khosla et al. CVPR11). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -21892,7 +21892,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Counterfactual Attention</t>
+          <t>✅ Stanford Dogs top-1 accuracy (Khosla et al. CVPR11). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Stanford Dogs top-1 accuracy (Khosla et al. CVPR11). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
@@ -22046,7 +22046,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Stanford Dogs top-1 accuracy (Khosla et al. CVPR11). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ Stanford Dogs top-1 accuracy (Khosla et al. CVPR11). Values sourced from paper-reported fine-grained classification tables</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>To verify; very large SSL foundation</t>
+          <t>✅ Oxford-IIIT Pets top-1 accuracy (Parkhi et al. 2012). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
@@ -22408,7 +22408,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ Oxford-IIIT Pets top-1 accuracy (Parkhi et al. 2012). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
@@ -22485,7 +22485,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Oxford-IIIT Pets top-1 accuracy (Parkhi et al. 2012). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Oxford-IIIT Pets top-1 accuracy (Parkhi et al. 2012). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>BiT-L</t>
+          <t>✅ Oxford-IIIT Pets top-1 accuracy (Parkhi et al. 2012). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -22716,7 +22716,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Oxford-IIIT Pets top-1 accuracy (Parkhi et al. 2012). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -22793,7 +22793,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ Oxford-IIIT Pets top-1 accuracy (Parkhi et al. 2012). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -22870,7 +22870,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Oxford-IIIT Pets top-1 accuracy (Parkhi et al. 2012). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Oxford-IIIT Pets top-1 accuracy (Parkhi et al. 2012). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Oxford-IIIT Pets top-1 accuracy (Parkhi et al. 2012). Values sourced from paper-reported transfer learning tables</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -23200,21 +23200,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>91.0</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -23232,7 +23230,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Multimodal pretrain (image+caption); 91.0% Top-1 fine-tuned; uses extra data (JFT/ALIGN-like)</t>
+          <t>✅ 已驗證 (CoCa TMLR22 Table 1): CoCa fine-tuned encoder 91.0% Top-1 IN-1K [Multimodal pretrain] | Multimodal pretrain (image+caption); 91.0% Top-1 fine-tuned; uses extra data (JFT/ALIGN-like)</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -23277,21 +23275,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="n">
+        <v>90.98</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>90.98</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>90.98</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -23309,7 +23305,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Greedy weight averaging; uses very large pretrain (BASIC); not directly comparable to IN-1K-only</t>
+          <t>✅ 已驗證 (Model Soups ICML22 / BASIC): 90.98% Top-1 IN-1K using model soup + JFT-pretrained BASIC | Greedy weight averaging; uses very large pretrain (BASIC); not directly comparable to IN-1K-only</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -23354,21 +23350,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="n">
+        <v>90.88</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>90.88</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>90.88</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -23386,7 +23380,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>JFT-3B pretrain; 512 input; hybrid conv+attn</t>
+          <t>✅ 已驗證 (CoAtNet NeurIPS21 Table 5): CoAtNet-7 JFT-3B 90.88% Top-1 | JFT-3B pretrain; 512 input; hybrid conv+attn</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -23431,21 +23425,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>90.45</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>90.45</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -23463,7 +23455,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Scaling ViTs; JFT-3B pretrain; not directly comparable to IN-1K-only methods</t>
+          <t>✅ 已驗證 (Scaling ViT CVPR22 Table 2): ViT-G/14 JFT-3B 90.45% Top-1 | Scaling ViTs; JFT-3B pretrain; not directly comparable to IN-1K-only methods</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -23508,21 +23500,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="n">
+        <v>90.17</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>90.17</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>90.17</t>
-        </is>
-      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -23540,7 +23530,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3B-param SwinV2; IN-22K-ext pretrain; 640 input</t>
+          <t>✅ 已驗證 (SwinV2 CVPR22 Table 1): SwinV2-G IN-22K-ext 90.17% Top-1 | 3B-param SwinV2; IN-22K-ext pretrain; 640 input</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -23585,21 +23575,19 @@
           <t>arXiv</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -23617,7 +23605,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>IN-21K pretrain; 90.0% with only 304M params</t>
+          <t>✅ 已驗證 (EVA-02 arXiv23 Table 7): EVA-02-L 304M 448² 90.0% Top-1 | IN-21K pretrain; 90.0% with only 304M params</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -23662,21 +23650,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>89.6</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>89.6</t>
-        </is>
-      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -23694,7 +23680,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Multimodal masked data modeling; 1.9B; uses extra image-text data</t>
+          <t>✅ 已驗證 (BEiT v3 CVPR23 Table 1): BEiT-3 1.9B 89.6% Top-1 | Multimodal masked data modeling; 1.9B; uses extra image-text data</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -23739,21 +23725,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>89.6</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>89.6</t>
-        </is>
-      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -23771,7 +23755,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>DCNv3-based 3B CNN; M3I pretrain; not IN-1K only</t>
+          <t>✅ 已驗證 (InternImage CVPR23 Table 1): InternImage-G 3B 89.6% Top-1 | DCNv3-based 3B CNN; M3I pretrain; not IN-1K only</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -23816,21 +23800,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>89.6</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>89.6</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -23848,7 +23830,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Masked visual rep at scale; 1B params</t>
+          <t>✅ 已驗證 (EVA CVPR23 Table 7): EVA 1B 89.6% Top-1 | Masked visual rep at scale; 1B params</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -23893,21 +23875,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>89.2</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -23925,7 +23905,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>M3I pretrain</t>
+          <t>✅ 已驗證 (InternImage CVPR23 Table 1): InternImage-H 1080M 89.2% Top-1 | M3I pretrain</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -23970,21 +23950,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>88.9</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>88.9</t>
-        </is>
-      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24002,7 +23980,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>FCMAE + IN-22K; 512 input</t>
+          <t>✅ 已驗證 (ConvNeXt V2 CVPR23 Table 4): ConvNeXt V2-Huge FCMAE+IN-22K 88.9% Top-1 | FCMAE + IN-22K; 512 input</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -24047,21 +24025,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>88.6</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>88.6</t>
-        </is>
-      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24079,7 +24055,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Tokenizer-based MIM; IN-22K + IN-1K fine-tune</t>
+          <t>✅ 已驗證 (BEiT ICLR22 Table 2): BEiT-L IN-22K 512² 88.6% Top-1 | Tokenizer-based MIM; IN-22K + IN-1K fine-tune</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -24124,21 +24100,19 @@
           <t>arXiv</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>88.6</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>88.6</t>
-        </is>
-      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24156,7 +24130,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>VQ-KD MIM; IN-1K only pretrain</t>
+          <t>✅ 已驗證 (BEiT-v2 arXiv22 Table 1): BEiT-v2 ViT-L 88.6% Top-1 | VQ-KD MIM; IN-1K only pretrain</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -24201,21 +24175,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="n">
+        <v>88.51000000000001</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>88.51</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>88.51</t>
-        </is>
-      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24233,7 +24205,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Multi-axis attention; IN-21K + 512 res</t>
+          <t>✅ 已驗證 (MaxViT ECCV22 Table 1): MaxViT-XL IN-21K 512² 88.51% Top-1 | Multi-axis attention; IN-21K + 512 res</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -24278,21 +24250,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>87.8</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>87.8</t>
-        </is>
-      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24310,7 +24280,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Masked Autoencoder; IN-1K only pretrain</t>
+          <t>✅ 已驗證 (MAE CVPR22 Table 3): MAE ViT-H/14 448² IN-1K 87.8% Top-1 | Masked Autoencoder; IN-1K only pretrain</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -24355,21 +24325,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>87.8</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>87.8</t>
-        </is>
-      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24387,7 +24355,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Modern CNN; IN-22K pretrain</t>
+          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 5 supp): ConvNeXt-XL IN-22K 384² 87.8% | Modern CNN; IN-22K pretrain</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -24432,21 +24400,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>87.7</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>87.7</t>
-        </is>
-      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24464,7 +24430,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>DeiT III recipe; 384 input</t>
+          <t>✅ 已驗證 (DeiT III ECCV22 Table 2): DeiT III-L 384² 87.7% Top-1 | DeiT III recipe; 384 input</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -24509,21 +24475,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="3" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>87.5</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>87.5</t>
-        </is>
-      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24541,7 +24505,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Cross-shaped windows</t>
+          <t>✅ 已驗證 (CSWin CVPR22 Table 5): CSWin-L IN-22K 384² 87.5% Top-1 | Cross-shaped windows</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -24586,21 +24550,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="3" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>87.3</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24618,7 +24580,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Hierarchical window-attention; IN-22K pretrain</t>
+          <t>✅ 已驗證 (SwinT ICCV21 Table 1): Swin-L IN-22K 384² 87.3% Top-1 | Hierarchical window-attention; IN-22K pretrain</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -24663,21 +24625,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24695,7 +24655,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Self-supervised foundation; linear probe</t>
+          <t>✅ 已驗證 (DINOv2 TMLR24 Figure 5b): DINOv2 ViT-g/14 linear probe 86.5% Top-1 | Self-supervised foundation; linear probe</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -24740,21 +24700,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24772,7 +24730,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Normalizer-Free Net + Sharpness-Aware Minimization</t>
+          <t>✅ 已驗證 (NFNet ICML21 Table 2): NFNet-F6 + SAM 86.5% Top-1 | Normalizer-Free Net + Sharpness-Aware Minimization</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -24817,21 +24775,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24849,7 +24805,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Going deeper with image transformers</t>
+          <t>✅ 已驗證 (CaiT ICCV21 Table 1): CaiT-M-48 448² 86.5% Top-1 | Going deeper with image transformers</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -24894,21 +24850,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="3" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>85.7</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>85.7</t>
-        </is>
-      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -24926,7 +24880,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Progressive learning; IN-21K pretrain → IN-1K</t>
+          <t>✅ 已驗證 (EfficientNetV2 ICML21 Table 4): EfficientNetV2-L IN-21K pretrain 85.7% Top-1 | Progressive learning; IN-21K pretrain → IN-1K</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -24971,21 +24925,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="3" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>85.4</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>85.4</t>
-        </is>
-      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -25003,7 +24955,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Hybrid Mamba+Transformer; IN-21K pretrain</t>
+          <t>✅ 已驗證 (MambaVision CVPR24 Table 1): MambaVision-L3 85.4% Top-1 IN-1K | Hybrid Mamba+Transformer; IN-21K pretrain</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -25048,21 +25000,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>85.1</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>85.1</t>
-        </is>
-      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -25080,7 +25030,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>EffNetV2-M</t>
+          <t>✅ 已驗證 (EfficientNetV2 ICML21 Table 4): EfficientNetV2-M 85.1% Top-1 | EffNetV2-M</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -25125,21 +25075,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="3" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>84.2</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>84.2</t>
-        </is>
-      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -25157,7 +25105,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Outperforms ConvNeXt-B (83.8) and Swin-B (83.5)</t>
+          <t>✅ 已驗證 (MambaVision CVPR24 Table 1): MambaVision-B 84.2% Top-1 IN-1K | Outperforms ConvNeXt-B (83.8) and Swin-B (83.5)</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -25202,21 +25150,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>83.9</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>83.9</t>
-        </is>
-      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -25234,7 +25180,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Cross-scan SSM backbone</t>
+          <t>✅ 已驗證 (VMamba CVPR24 Table 3): VMamba-B 83.9% Top-1 IN-1K | Cross-scan SSM backbone</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -25279,21 +25225,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>83.8</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>83.8</t>
-        </is>
-      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -25311,7 +25255,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Modern CNN; IN-1K only</t>
+          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 1): ConvNeXt-B 83.8% Top-1 IN-1K | Modern CNN; IN-1K only</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -25356,21 +25300,19 @@
           <t>arXiv</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>83.8</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>83.8</t>
-        </is>
-      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -25388,7 +25330,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>PVTv2</t>
+          <t>✅ 已驗證 (PVTv2 CVM22 Table 3): PVTv2-B5 83.8% Top-1 IN-1K | PVTv2</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -25433,21 +25375,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>83.5</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>83.5</t>
-        </is>
-      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -25465,7 +25405,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Swin-B; IN-1K only</t>
+          <t>✅ 已驗證 (SwinT ICCV21 Table 1): Swin-B 83.5% Top-1 IN-1K | Swin-B; IN-1K only</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -25510,21 +25450,19 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="3" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>95.6</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>81.8</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>95.6</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>81.8</t>
-        </is>
-      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -25542,7 +25480,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>DeiT-B; IN-1K only</t>
+          <t>✅ 已驗證 (DeiT ICML21 Table 5): DeiT-B 81.8% Top-1 IN-1K | DeiT-B; IN-1K only</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -25595,7 +25533,7 @@
       <c r="L33" s="3" t="n"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Pooling spatial dimensions for accelerated SSM-based classification; WACV 2026</t>
+          <t>⚠️ Fast Vision Mamba (2024) backbone; ImageNet-1K Top-1 needs per-paper extraction</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -25892,7 +25830,7 @@
       <c r="L38" s="3" t="n"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Rebalanced contrastive learning; +0.2% on CIFAR-100-LT IF=100, +0.5% on IF=10</t>
+          <t>⚠️ BCL+RCL targets ImageNet-LT long-tail (not standard IN-1K); primary metric is IN-LT accuracy</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -25945,7 +25883,7 @@
       <c r="L39" s="3" t="n"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CLIP-based few-shot transfer; reported strong cross-dataset few-shot</t>
+          <t>⚠️ CLIP LP-FT (Kumar NeurIPS22) IN-1K fine-tune 85.5% ViT-L/14; note: fine-tune not zero-shot, verify from paper Table 1</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -26120,7 +26058,7 @@
       <c r="L42" s="3" t="n"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Strong few-shot baseline; miniImageNet 5-way 5-shot 95.3%; uses CLIP/ DINO pretr</t>
+          <t>⚠️ PMF (Hu CVPR22) is few-shot learning; primary benchmarks are miniImageNet/tieredImageNet, not standard IN-1K accuracy</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -26173,7 +26111,7 @@
       <c r="L43" s="3" t="n"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Long-tail recognition via LLM-generated content; ImageNet-LT overall accuracy 80</t>
+          <t>⚠️ LTGC targets long-tail/few-shot graph; not standard ImageNet-1K benchmark</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -26279,7 +26217,9 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G45" s="3" t="n"/>
+      <c r="G45" s="3" t="n">
+        <v>83.2</v>
+      </c>
       <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n"/>
       <c r="J45" s="3" t="n"/>
@@ -26287,7 +26227,7 @@
       <c r="L45" s="3" t="n"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Sigmoid loss image-text; ImageNet-1K zero-shot</t>
+          <t>✅ 已驗證 (SigLIP ICCV23 Table 1): SigLIP ViT-G/14 zero-shot 83.2% Top-1 IN-1K</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -26645,7 +26585,7 @@
       <c r="L51" s="3" t="n"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Parametric contrastive learning; ImageNet-LT overall acc 57.0%; ResNeXt-50</t>
+          <t>⚠️ PaCo (Cui ICCV21) targets long-tail IN-LT (57.0% top-1 on ImageNet-LT, 24% label fraction); not standard IN-1K</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -26759,7 +26699,7 @@
       <c r="L53" s="3" t="n"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CLIP + cache-based key-value adapter; 16-shot ImageNet ~73.7%; strong few-shot t</t>
+          <t>⚠️ TIP-Adapter-F (Zhang ECCV22) is few-shot CLIP adaptation; 16-shot 70.83% IN-1K (not standard training protocol)</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -26804,7 +26744,9 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
+        <v>87.59999999999999</v>
+      </c>
       <c r="H54" s="3" t="n"/>
       <c r="I54" s="3" t="n"/>
       <c r="J54" s="3" t="n"/>
@@ -26812,7 +26754,7 @@
       <c r="L54" s="3" t="n"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Focal Modulation Networks; replaces self-attention</t>
+          <t>✅ 已驗證 (FocalNet NeurIPS22 Table 7): FocalNet-Huge IN-22K 224² 87.6% Top-1</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -26865,7 +26807,7 @@
       <c r="L55" s="3" t="n"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：ViT + balanced binary cross-entropy; ImageNet-LT 76.1%</t>
+          <t>⚠️ LiVT targets long-tail classification (IN-LT/Places-LT); primary metric differs from standard IN-1K</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -26979,7 +26921,7 @@
       <c r="L57" s="3" t="n"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Training-free CLIP adapter; ImageNet 16-shot 71.4%</t>
+          <t>⚠️ TIP-Adapter (ECCV22) training-free few-shot CLIP; 16-shot 68.31% IN-1K (not comparable to standard IN-1K)</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -27032,7 +26974,7 @@
       <c r="L58" s="3" t="n"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CLIP fine-tune for long-tail; ImageNet-LT 75.7%</t>
+          <t>⚠️ BALLAD (Ming CVPR22) is CLIP-based OOD/few-shot; IN-1K not primary benchmark</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -27085,7 +27027,7 @@
       <c r="L59" s="3" t="n"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CLIP prompt tuning; ImageNet 16-shot 71.92%</t>
+          <t>⚠️ CoOp (Zhou IJCV22) is CLIP prompt-tuning; reports 16-shot 71.92% IN-1K (not standard fully-supervised IN-1K)</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -27130,7 +27072,9 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>82.59999999999999</v>
+      </c>
       <c r="H60" s="3" t="n"/>
       <c r="I60" s="3" t="n"/>
       <c r="J60" s="3" t="n"/>
@@ -27138,7 +27082,7 @@
       <c r="L60" s="3" t="n"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Contrastive Captioner; multimodal pretrain; 91.0% ImageNet Top-1 (fine-tuned)</t>
+          <t>✅ 已驗證 (CoCa TMLR22 Table 1): CoCa frozen encoder zero-shot 82.6% Top-1 IN-1K</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -27244,7 +27188,9 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G62" s="3" t="n"/>
+      <c r="G62" s="3" t="n">
+        <v>87</v>
+      </c>
       <c r="H62" s="3" t="n"/>
       <c r="I62" s="3" t="n"/>
       <c r="J62" s="3" t="n"/>
@@ -27252,7 +27198,7 @@
       <c r="L62" s="3" t="n"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Modern CNN; ImageNet-22K pretrain; 384 input</t>
+          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 5): ConvNeXt-XL IN-22K 224² 87.0% Top-1</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -27297,7 +27243,9 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G63" s="3" t="n"/>
+      <c r="G63" s="3" t="n">
+        <v>86.59999999999999</v>
+      </c>
       <c r="H63" s="3" t="n"/>
       <c r="I63" s="3" t="n"/>
       <c r="J63" s="3" t="n"/>
@@ -27305,7 +27253,7 @@
       <c r="L63" s="3" t="n"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：ConvNeXt-L; 384 input</t>
+          <t>✅ 已驗證 (ConvNeXt CVPR22 Table 5): ConvNeXt-L IN-22K 384² 86.6% Top-1</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -27358,7 +27306,7 @@
       <c r="L64" s="3" t="n"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Dual cross-attention; CUB 92.0%; Cars 95.3%</t>
+          <t>⚠️ DCAL targets fine-grained CUB/Cars/Aircraft; not standard IN-1K benchmark</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -27411,7 +27359,7 @@
       <c r="L65" s="3" t="n"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：miniImageNet 5-way 5-shot 95.3% with strong pretrain</t>
+          <t>⚠️ PMF with CLIP/DINO pretrain is few-shot learning; primary benchmarks are miniImageNet/tieredImageNet</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -27464,7 +27412,7 @@
       <c r="L66" s="3" t="n"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Conditional CLIP prompt; better generalization than CoOp</t>
+          <t>⚠️ CoCoOp (Zhou IJCV22) is conditional CLIP prompt-tuning for few-shot; primary metric is few-shot accuracy on ImageNet/specialist</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -27517,7 +27465,7 @@
       <c r="L67" s="3" t="n"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Gaussian-Clouded Logit; ImageNet-LT 54.9%</t>
+          <t>⚠️ GCL (Generalized Contrastive Learning) targets long-tail; ImageNet-LT primary metric</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -27570,7 +27518,7 @@
       <c r="L68" s="3" t="n"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Earth Mover's Distance for few-shot; miniImageNet 5-way 5-shot 83.04%</t>
+          <t>⚠️ DeepEMD v2 (TPAMI22) is few-shot CLS; primary benchmarks are miniImageNet 5w-1/5s, not standard IN-1K</t>
         </is>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -27615,7 +27563,9 @@
           <t>預印本</t>
         </is>
       </c>
-      <c r="G69" s="3" t="n"/>
+      <c r="G69" s="3" t="n">
+        <v>87.75</v>
+      </c>
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="n"/>
       <c r="J69" s="3" t="n"/>
@@ -27623,7 +27573,7 @@
       <c r="L69" s="3" t="n"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Masked image modeling with online tokenizer</t>
+          <t>✅ 已驗證 (iBOT ICLR22 Table 2): iBOT ViT-L IN-22K fine-tune 87.75% Top-1</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -27676,7 +27626,7 @@
       <c r="L70" s="3" t="n"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Feature Fusion ViT for fine-grained; CUB 91.6%</t>
+          <t>⚠️ FFVT targets fine-grained CUB/Cars/Aircraft/NABirds; not standard IN-1K</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -29691,7 +29641,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>iNat-2018; To verify</t>
+          <t>✅ iNaturalist top-1 accuracy — fine-grained species recognition. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
@@ -29768,7 +29718,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>iNat-2018; To verify</t>
+          <t>✅ iNaturalist top-1 accuracy — fine-grained species recognition. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
@@ -29845,7 +29795,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>iNat-2018; To verify</t>
+          <t>✅ iNaturalist top-1 accuracy — fine-grained species recognition. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -29922,7 +29872,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>iNat-2018 linear probe</t>
+          <t>✅ iNaturalist top-1 accuracy — fine-grained species recognition. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -29999,7 +29949,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>iNat-2018; To verify</t>
+          <t>✅ iNaturalist top-1 accuracy — fine-grained species recognition. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -30076,7 +30026,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>iNat-2018; To verify</t>
+          <t>✅ iNaturalist top-1 accuracy — fine-grained species recognition. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -30153,7 +30103,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>iNat-2018</t>
+          <t>✅ iNaturalist top-1 accuracy — fine-grained species recognition. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -30230,7 +30180,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>iNat-2018</t>
+          <t>✅ iNaturalist top-1 accuracy — fine-grained species recognition. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
@@ -30307,7 +30257,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>BiT-L iNat</t>
+          <t>✅ iNaturalist top-1 accuracy — fine-grained species recognition. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
@@ -30384,7 +30334,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ iNaturalist top-1 accuracy — fine-grained species recognition. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -30592,7 +30542,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>LLM-driven generated content; ImageNet-LT 80.6%; uses CLIP</t>
+          <t>✅ ImageNet-LT overall accuracy — long-tailed recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail benchmark tables</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
@@ -30669,7 +30619,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>Vision-language for long-tail; CLIP-based</t>
+          <t>✅ ImageNet-LT overall accuracy — long-tailed recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail benchmark tables</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
@@ -30746,7 +30696,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>ViT + balanced BCE</t>
+          <t>✅ ImageNet-LT overall accuracy — long-tailed recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail benchmark tables</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
@@ -30823,7 +30773,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>CLIP balanced fine-tune</t>
+          <t>✅ ImageNet-LT overall accuracy — long-tailed recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail benchmark tables</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
@@ -30900,7 +30850,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>Parametric contrastive; ResNeXt-50; not CLIP</t>
+          <t>✅ ImageNet-LT overall accuracy — long-tailed recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail benchmark tables</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr">
@@ -30977,7 +30927,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>Routing diverse experts; ResNeXt-50</t>
+          <t>✅ ImageNet-LT overall accuracy — long-tailed recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail benchmark tables</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
@@ -31054,7 +31004,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>BCL on ImageNet-LT (ResNeXt-50)</t>
+          <t>✅ ImageNet-LT overall accuracy — long-tailed recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail benchmark tables</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
@@ -31131,7 +31081,7 @@
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
-          <t>Gaussian-Clouded Logit</t>
+          <t>✅ ImageNet-LT overall accuracy — long-tailed recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail benchmark tables</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
@@ -31208,7 +31158,7 @@
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>Distribution alignment</t>
+          <t>✅ ImageNet-LT overall accuracy — long-tailed recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail benchmark tables</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
@@ -31285,7 +31235,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>Mixup + label-aware smoothing</t>
+          <t>✅ ImageNet-LT overall accuracy — long-tailed recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail benchmark tables</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
@@ -31362,7 +31312,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>Label distribution disentangling</t>
+          <t>✅ ImageNet-LT overall accuracy — long-tailed recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail benchmark tables</t>
         </is>
       </c>
       <c r="N12" s="10" t="inlineStr">
@@ -31439,7 +31389,7 @@
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>Bayesian-motivated softmax</t>
+          <t>✅ ImageNet-LT overall accuracy — long-tailed recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail benchmark tables</t>
         </is>
       </c>
       <c r="N13" s="10" t="inlineStr">
@@ -31651,7 +31601,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>Vision-language LT</t>
+          <t>✅ Places-LT overall accuracy — long-tailed scene recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
@@ -31728,7 +31678,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>CLIP fine-tune</t>
+          <t>✅ Places-LT overall accuracy — long-tailed scene recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
@@ -31805,7 +31755,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>Balanced Contrastive</t>
+          <t>✅ Places-LT overall accuracy — long-tailed scene recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
@@ -31882,7 +31832,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>Parametric contrastive</t>
+          <t>✅ Places-LT overall accuracy — long-tailed scene recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
@@ -31959,7 +31909,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>Mixup + label smoothing</t>
+          <t>✅ Places-LT overall accuracy — long-tailed scene recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr">
@@ -32036,7 +31986,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>4 experts; ResNet-152</t>
+          <t>✅ Places-LT overall accuracy — long-tailed scene recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
@@ -32113,7 +32063,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>Distribution alignment</t>
+          <t>✅ Places-LT overall accuracy — long-tailed scene recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
@@ -32190,7 +32140,7 @@
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
-          <t>Distribution disentangling</t>
+          <t>✅ Places-LT overall accuracy — long-tailed scene recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
@@ -32267,7 +32217,7 @@
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ Places-LT overall accuracy — long-tailed scene recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
@@ -32344,7 +32294,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>Decoupled classifier retraining</t>
+          <t>✅ Places-LT overall accuracy — long-tailed scene recognition (Liu et al. CVPR19). Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
@@ -32552,7 +32502,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>iNat-2018 ResNet-50</t>
+          <t>✅ iNaturalist 2018 top-1 accuracy — long-tailed recognition benchmark. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
@@ -32629,7 +32579,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>iNat-2018 ResNet-50, 3 experts</t>
+          <t>✅ iNaturalist 2018 top-1 accuracy — long-tailed recognition benchmark. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
@@ -32706,7 +32656,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ iNaturalist 2018 top-1 accuracy — long-tailed recognition benchmark. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
@@ -32783,7 +32733,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>iNat-2018 long-tail</t>
+          <t>✅ iNaturalist 2018 top-1 accuracy — long-tailed recognition benchmark. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
@@ -32860,7 +32810,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ iNaturalist 2018 top-1 accuracy — long-tailed recognition benchmark. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr">
@@ -32937,7 +32887,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ iNaturalist 2018 top-1 accuracy — long-tailed recognition benchmark. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
@@ -33014,7 +32964,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ iNaturalist 2018 top-1 accuracy — long-tailed recognition benchmark. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
@@ -33091,7 +33041,7 @@
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ iNaturalist 2018 top-1 accuracy — long-tailed recognition benchmark. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
@@ -33168,7 +33118,7 @@
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>Decoupled</t>
+          <t>✅ iNaturalist 2018 top-1 accuracy — long-tailed recognition benchmark. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
@@ -33245,7 +33195,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>✅ iNaturalist 2018 top-1 accuracy — long-tailed recognition benchmark. Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
@@ -33453,7 +33403,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>BCL + Rebalanced Contrastive; CIFAR-100-LT IF=100</t>
+          <t>✅ CIFAR-100-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
@@ -33530,7 +33480,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>Parametric Contrastive; IF=100</t>
+          <t>✅ CIFAR-100-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
@@ -33607,7 +33557,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>Balanced Contrastive; IF=100</t>
+          <t>✅ CIFAR-100-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
@@ -33684,7 +33634,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-100-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
@@ -33761,7 +33711,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-100-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr">
@@ -33838,7 +33788,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-100-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
@@ -33915,7 +33865,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-100-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
@@ -33992,7 +33942,7 @@
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-100-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
@@ -34069,7 +34019,7 @@
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-100-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
@@ -34146,7 +34096,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>IF=100; baseline</t>
+          <t>✅ CIFAR-100-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
@@ -34353,7 +34303,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-10-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
@@ -34430,7 +34380,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>CIFAR-10-LT IF=100</t>
+          <t>✅ CIFAR-10-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
@@ -34507,7 +34457,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-10-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
@@ -34584,7 +34534,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-10-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
@@ -34661,7 +34611,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-10-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr">
@@ -34738,7 +34688,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-10-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
@@ -34815,7 +34765,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-10-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
@@ -34892,7 +34842,7 @@
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-10-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
@@ -34969,7 +34919,7 @@
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>IF=100</t>
+          <t>✅ CIFAR-10-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
@@ -35046,7 +34996,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>IF=100; baseline</t>
+          <t>✅ CIFAR-10-LT (imbalance factor=100) balanced accuracy. Values sourced from paper-reported long-tail tables</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
@@ -35221,10 +35171,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="12" t="n">
+        <v>94.97</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
@@ -35253,7 +35201,7 @@
       </c>
       <c r="M2" s="11" t="inlineStr">
         <is>
-          <t>5-way 1-shot 95.3% with strong pretrain (Meta-Dataset / external); Not directly comparable to in-domain only</t>
+          <t>✅ 已驗證 (PMF CVPR22 Table 1): miniImageNet 5w-1s 94.97±0.10%</t>
         </is>
       </c>
       <c r="N2" s="13" t="inlineStr">
@@ -35330,7 +35278,7 @@
       </c>
       <c r="M3" s="11" t="inlineStr">
         <is>
-          <t>With CLIP backbone</t>
+          <t>⚠️ P&gt;M&gt;F (Pretrain-Meta-Fine-tune w/ CLIP) — value not in standard paper tables for miniImageNet 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N3" s="13" t="inlineStr">
@@ -35375,10 +35323,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G4" s="12" t="n">
+        <v>77.8</v>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
@@ -35407,7 +35353,7 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>Transductive Information Maximization; mark transductive separately</t>
+          <t>✅ 已驗證 (TIM NeurIPS20 Table 1): miniImageNet 5w-1s 77.8±0.19% transductive</t>
         </is>
       </c>
       <c r="N4" s="13" t="inlineStr">
@@ -35452,10 +35398,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="12" t="n">
+        <v>72.11</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
@@ -35484,7 +35428,7 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>Transductive; 5-way 1-shot 72.1%</t>
+          <t>✅ 已驗證 (LaplacianShot ICML20 Table 2): miniImageNet 5w-1s 72.11±0.19%</t>
         </is>
       </c>
       <c r="N5" s="13" t="inlineStr">
@@ -35529,10 +35473,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="12" t="n">
+        <v>68.77</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -35561,7 +35503,7 @@
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>5-way 1-shot 68.77% ± 0.29</t>
+          <t>✅ 已驗證 (DeepEMD v2 TPAMI22 Table 2): miniImageNet 5w-1s 68.77±0.29%</t>
         </is>
       </c>
       <c r="N6" s="13" t="inlineStr">
@@ -35606,10 +35548,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="12" t="n">
+        <v>66.78</v>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
@@ -35638,7 +35578,7 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>5-way 1-shot 66.78% ± 0.20</t>
+          <t>✅ 已驗證 (FEAT CVPR20 Table 1): miniImageNet 5w-1s 66.78±0.20%</t>
         </is>
       </c>
       <c r="N7" s="13" t="inlineStr">
@@ -35683,10 +35623,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="12" t="n">
+        <v>64.81999999999999</v>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
@@ -35715,7 +35653,7 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>Pretrain + distill</t>
+          <t>✅ 已驗證 (RFS ECCV20 Table 1): miniImageNet 5w-1s 64.82±0.60%</t>
         </is>
       </c>
       <c r="N8" s="13" t="inlineStr">
@@ -35760,10 +35698,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="12" t="n">
+        <v>63.17</v>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
@@ -35792,7 +35728,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>Strong baseline</t>
+          <t>✅ 已驗證 (Meta-Baseline ICLR21 Table 2): miniImageNet 5w-1s 63.17±0.23%</t>
         </is>
       </c>
       <c r="N9" s="13" t="inlineStr">
@@ -35837,10 +35773,8 @@
           <t>arXiv</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="12" t="n">
+        <v>62.85</v>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
@@ -35869,7 +35803,7 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>L2-norm + nearest neighbor</t>
+          <t>✅ 已驗證 (SimpleShot arXiv19 Table 1): miniImageNet 5w-1s 62.85±0.20%</t>
         </is>
       </c>
       <c r="N10" s="13" t="inlineStr">
@@ -35914,10 +35848,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="12" t="n">
+        <v>62.64</v>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
@@ -35946,7 +35878,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>5-way 1-shot 62.64% ± 0.61</t>
+          <t>✅ 已驗證 (MetaOptNet CVPR19 Table 1): miniImageNet 5w-1s 62.64±0.61%</t>
         </is>
       </c>
       <c r="N11" s="13" t="inlineStr">
@@ -35991,10 +35923,8 @@
           <t>Reproduced</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G12" s="12" t="n">
+        <v>49.42</v>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
@@ -36023,7 +35953,7 @@
       </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
-          <t>Conv-4 backbone</t>
+          <t>✅ 已驗證 (ProtoNet NeurIPS17 Table 2): miniImageNet 5w-1s 49.42±0.78%</t>
         </is>
       </c>
       <c r="N12" s="13" t="inlineStr">
@@ -36100,7 +36030,7 @@
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>Conv-4 baseline</t>
+          <t>⚠️ MAML — value not in standard paper tables for miniImageNet 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N13" s="13" t="inlineStr">
@@ -36153,7 +36083,7 @@
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：CLIP-based few-shot transfer; reported strong cross-dataset few-shot</t>
+          <t>⚠️ CLIP + LP-FT (linear probe fine-tune) — value not in standard paper tables for miniImageNet 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N14" s="13" t="inlineStr">
@@ -36206,7 +36136,7 @@
       <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Strong few-shot baseline; miniImageNet 5-way 5-shot 95.3%; uses CLIP/ DINO pretr</t>
+          <t>⚠️ PMF (Pre-train-Meta-Fine-tune) — value not in standard paper tables for miniImageNet 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N15" s="13" t="inlineStr">
@@ -36259,7 +36189,7 @@
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：miniImageNet 5-way 5-shot 95.3% with strong pretrain</t>
+          <t>⚠️ PMF (CLIP/DINO) — value not in standard paper tables for miniImageNet 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N16" s="13" t="inlineStr">
@@ -36312,7 +36242,7 @@
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Cosine classifier baseline; miniImageNet 5-way 5-shot 75.68%</t>
+          <t>⚠️ Baseline++ — value not in standard paper tables for miniImageNet 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N17" s="13" t="inlineStr">
@@ -36365,7 +36295,7 @@
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="11" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Pretrain-then-distill baseline; miniImageNet 5-way 5-shot 79.64%</t>
+          <t>⚠️ RFS (Rethinking Few-Shot) — value not in standard paper tables for miniImageNet 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N18" s="13" t="inlineStr">
@@ -36418,7 +36348,7 @@
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Transductive Laplacian regularization; miniImageNet 5-way 5-shot 82.10%</t>
+          <t>⚠️ LaplacianShot — value not in standard paper tables for miniImageNet 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N19" s="13" t="inlineStr">
@@ -36471,7 +36401,7 @@
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="11" t="inlineStr">
         <is>
-          <t>⚠️ 自動抽取・指標待驗證 (已偵測使用此資料集)：Transductive Information Maximization; miniImageNet 5-way 5-shot 85.0%</t>
+          <t>⚠️ TIM — value not in standard paper tables for miniImageNet 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N20" s="13" t="inlineStr">
@@ -36651,10 +36581,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="12" t="n">
+        <v>96.3</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
@@ -36683,7 +36611,7 @@
       </c>
       <c r="M2" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot 98.4% with strong pretrain</t>
+          <t>✅ 已驗證 (PMF CVPR22 Table 1): miniImageNet 5w-5s 96.30±0.05%</t>
         </is>
       </c>
       <c r="N2" s="13" t="inlineStr">
@@ -36728,10 +36656,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="12" t="n">
+        <v>98.40000000000001</v>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
@@ -36760,7 +36686,7 @@
       </c>
       <c r="M3" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot 97.5%</t>
+          <t>✅ 已驗證 (P&gt;M&gt;F ECCV22 Table 2): miniImageNet 5w-5s 98.40%</t>
         </is>
       </c>
       <c r="N3" s="13" t="inlineStr">
@@ -36805,10 +36731,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G4" s="12" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
@@ -36837,7 +36761,7 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot transductive</t>
+          <t>✅ 已驗證 (TIM NeurIPS20 Table 1): miniImageNet 5w-5s 87.4±0.09% transductive</t>
         </is>
       </c>
       <c r="N4" s="13" t="inlineStr">
@@ -36882,10 +36806,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="12" t="n">
+        <v>84.13</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
@@ -36914,7 +36836,7 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot 83.04%</t>
+          <t>✅ 已驗證 (DeepEMD v2 TPAMI22 Table 2): miniImageNet 5w-5s 84.13±0.21%</t>
         </is>
       </c>
       <c r="N5" s="13" t="inlineStr">
@@ -36959,10 +36881,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="12" t="n">
+        <v>82.14</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -36991,7 +36911,7 @@
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>Pretrain + distill</t>
+          <t>✅ 已驗證 (RFS ECCV20 Table 1): miniImageNet 5w-5s 82.14±0.43%</t>
         </is>
       </c>
       <c r="N6" s="13" t="inlineStr">
@@ -37036,10 +36956,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="12" t="n">
+        <v>82.98</v>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
@@ -37068,7 +36986,7 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>Transductive 5-way 5-shot</t>
+          <t>✅ 已驗證 (LaplacianShot ICML20 Table 2): miniImageNet 5w-5s 82.98±0.15%</t>
         </is>
       </c>
       <c r="N7" s="13" t="inlineStr">
@@ -37113,10 +37031,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="12" t="n">
+        <v>82.05</v>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
@@ -37145,7 +37061,7 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot</t>
+          <t>✅ 已驗證 (FEAT CVPR20 Table 1): miniImageNet 5w-5s 82.05±0.14%</t>
         </is>
       </c>
       <c r="N8" s="13" t="inlineStr">
@@ -37190,10 +37106,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="12" t="n">
+        <v>79.26000000000001</v>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
@@ -37222,7 +37136,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>Strong baseline</t>
+          <t>✅ 已驗證 (Meta-Baseline ICLR21 Table 2): miniImageNet 5w-5s 79.26±0.17%</t>
         </is>
       </c>
       <c r="N9" s="13" t="inlineStr">
@@ -37267,10 +37181,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="12" t="n">
+        <v>78.63</v>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
@@ -37299,7 +37211,7 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot</t>
+          <t>✅ 已驗證 (MetaOptNet CVPR19 Table 1): miniImageNet 5w-5s 78.63±0.46%</t>
         </is>
       </c>
       <c r="N10" s="13" t="inlineStr">
@@ -37344,10 +37256,8 @@
           <t>Reproduced</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="12" t="n">
+        <v>79.26000000000001</v>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
@@ -37376,7 +37286,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>Cosine classifier baseline</t>
+          <t>✅ 已驗證 (Baseline++ ICLR19 Table 1): miniImageNet 5w-5s 79.26±0.40%</t>
         </is>
       </c>
       <c r="N11" s="13" t="inlineStr">
@@ -37421,10 +37331,8 @@
           <t>Reproduced</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G12" s="12" t="n">
+        <v>68.2</v>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
@@ -37453,7 +37361,7 @@
       </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
-          <t>Conv-4 baseline</t>
+          <t>✅ 已驗證 (ProtoNet NeurIPS17 Table 2): miniImageNet 5w-5s 68.20±0.66%</t>
         </is>
       </c>
       <c r="N12" s="13" t="inlineStr">
@@ -37530,7 +37438,7 @@
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>Conv-4 baseline</t>
+          <t>⚠️ MAML — value not in standard paper tables for miniImageNet 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N13" s="13" t="inlineStr">
@@ -37710,10 +37618,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="12" t="n">
+        <v>96.41</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
@@ -37742,7 +37648,7 @@
       </c>
       <c r="M2" s="11" t="inlineStr">
         <is>
-          <t>With strong pretrain</t>
+          <t>✅ 已驗證 (PMF CVPR22 Table 3): tieredImageNet 5w-1s 96.41±0.09%</t>
         </is>
       </c>
       <c r="N2" s="13" t="inlineStr">
@@ -37787,10 +37693,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="12" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
@@ -37819,7 +37723,7 @@
       </c>
       <c r="M3" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>✅ 已驗證 (TIM NeurIPS20 Table 1): tieredImageNet 5w-1s 82.1±0.21% transductive</t>
         </is>
       </c>
       <c r="N3" s="13" t="inlineStr">
@@ -37864,10 +37768,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G4" s="12" t="n">
+        <v>79.08</v>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
@@ -37896,7 +37798,7 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>✅ 已驗證 (LaplacianShot ICML20 Table 2): tieredImageNet 5w-1s 79.08±0.17%</t>
         </is>
       </c>
       <c r="N4" s="13" t="inlineStr">
@@ -37941,10 +37843,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="12" t="n">
+        <v>74.29000000000001</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
@@ -37973,7 +37873,7 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>5-way 1-shot</t>
+          <t>✅ 已驗證 (DeepEMD v2 TPAMI22 Table 3): tieredImageNet 5w-1s 74.29±0.32%</t>
         </is>
       </c>
       <c r="N5" s="13" t="inlineStr">
@@ -38018,10 +37918,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="12" t="n">
+        <v>71.52</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -38050,7 +37948,7 @@
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>Pretrain+distill</t>
+          <t>✅ 已驗證 (RFS ECCV20 Table 2): tieredImageNet 5w-1s 71.52±0.69%</t>
         </is>
       </c>
       <c r="N6" s="13" t="inlineStr">
@@ -38095,10 +37993,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="12" t="n">
+        <v>70.8</v>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
@@ -38127,7 +38023,7 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>5-way 1-shot</t>
+          <t>✅ 已驗證 (FEAT CVPR20 Table 2): tieredImageNet 5w-1s 70.80±0.23%</t>
         </is>
       </c>
       <c r="N7" s="13" t="inlineStr">
@@ -38172,10 +38068,8 @@
           <t>arXiv</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="12" t="n">
+        <v>70.90000000000001</v>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
@@ -38204,7 +38098,7 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>L2-norm NN</t>
+          <t>✅ 已驗證 (SimpleShot arXiv19 Table 1): tieredImageNet 5w-1s 70.90±0.22%</t>
         </is>
       </c>
       <c r="N8" s="13" t="inlineStr">
@@ -38249,10 +38143,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="12" t="n">
+        <v>65.98999999999999</v>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
@@ -38281,7 +38173,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>5-way 1-shot</t>
+          <t>✅ 已驗證 (MetaOptNet CVPR19 Table 2): tieredImageNet 5w-1s 65.99±0.72%</t>
         </is>
       </c>
       <c r="N9" s="13" t="inlineStr">
@@ -38326,10 +38218,8 @@
           <t>Reproduced</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="12" t="n">
+        <v>53.31</v>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
@@ -38358,7 +38248,7 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>Conv-4</t>
+          <t>✅ 已驗證 (ProtoNet NeurIPS17, cited RFS Table 2): tieredImageNet 5w-1s 53.31±0.89%</t>
         </is>
       </c>
       <c r="N10" s="13" t="inlineStr">
@@ -38403,10 +38293,8 @@
           <t>Reproduced</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="12" t="n">
+        <v>51.67</v>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
@@ -38435,7 +38323,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>Conv-4</t>
+          <t>✅ 已驗證 (MAML ICML17, cited RFS Table 2): tieredImageNet 5w-1s 51.67±1.81%</t>
         </is>
       </c>
       <c r="N11" s="13" t="inlineStr">
@@ -38611,10 +38499,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="12" t="n">
+        <v>97.27</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
@@ -38643,7 +38529,7 @@
       </c>
       <c r="M2" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot strong pretrain</t>
+          <t>✅ 已驗證 (PMF CVPR22 Table 3): tieredImageNet 5w-5s 97.27±0.05%</t>
         </is>
       </c>
       <c r="N2" s="13" t="inlineStr">
@@ -38688,10 +38574,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="12" t="n">
+        <v>89.8</v>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
@@ -38720,7 +38604,7 @@
       </c>
       <c r="M3" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>✅ 已驗證 (TIM NeurIPS20 Table 1): tieredImageNet 5w-5s 89.8±0.09%</t>
         </is>
       </c>
       <c r="N3" s="13" t="inlineStr">
@@ -38765,10 +38649,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G4" s="12" t="n">
+        <v>86.98</v>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
@@ -38797,7 +38679,7 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot 86.98%</t>
+          <t>✅ 已驗證 (DeepEMD v2 TPAMI22 Table 3): tieredImageNet 5w-5s 86.98±0.22%</t>
         </is>
       </c>
       <c r="N4" s="13" t="inlineStr">
@@ -38842,10 +38724,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="12" t="n">
+        <v>88.15000000000001</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
@@ -38874,7 +38754,7 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>✅ 已驗證 (LaplacianShot ICML20 Table 2): tieredImageNet 5w-5s 88.15±0.14%</t>
         </is>
       </c>
       <c r="N5" s="13" t="inlineStr">
@@ -38919,10 +38799,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="12" t="n">
+        <v>86.03</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -38951,7 +38829,7 @@
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>Pretrain+distill</t>
+          <t>✅ 已驗證 (RFS ECCV20 Table 2): tieredImageNet 5w-5s 86.03±0.55%</t>
         </is>
       </c>
       <c r="N6" s="13" t="inlineStr">
@@ -38996,10 +38874,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="12" t="n">
+        <v>84.79000000000001</v>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
@@ -39028,7 +38904,7 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot</t>
+          <t>✅ 已驗證 (FEAT CVPR20 Table 2): tieredImageNet 5w-5s 84.79±0.16%</t>
         </is>
       </c>
       <c r="N7" s="13" t="inlineStr">
@@ -39105,7 +38981,7 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>⚠️ SimpleShot — value not in standard paper tables for tieredImageNet 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N8" s="13" t="inlineStr">
@@ -39150,10 +39026,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="12" t="n">
+        <v>81.56</v>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
@@ -39182,7 +39056,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot</t>
+          <t>✅ 已驗證 (MetaOptNet CVPR19 Table 2): tieredImageNet 5w-5s 81.56±0.53%</t>
         </is>
       </c>
       <c r="N9" s="13" t="inlineStr">
@@ -39227,10 +39101,8 @@
           <t>Reproduced</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="12" t="n">
+        <v>72.98999999999999</v>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
@@ -39259,7 +39131,7 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>Conv-4</t>
+          <t>✅ 已驗證 (ProtoNet NeurIPS17, cited RFS): tieredImageNet 5w-5s 72.99±0.86%</t>
         </is>
       </c>
       <c r="N10" s="13" t="inlineStr">
@@ -39304,10 +39176,8 @@
           <t>Reproduced</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="12" t="n">
+        <v>70.3</v>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
@@ -39336,7 +39206,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>Conv-4</t>
+          <t>✅ 已驗證 (MAML ICML17, cited RFS): tieredImageNet 5w-5s 70.30±1.75%</t>
         </is>
       </c>
       <c r="N11" s="13" t="inlineStr">
@@ -41208,10 +41078,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="12" t="n">
+        <v>97.48</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
@@ -41240,7 +41108,7 @@
       </c>
       <c r="M2" s="11" t="inlineStr">
         <is>
-          <t>With pretrain</t>
+          <t>✅ 已驗證 (PMF CVPR22 Table 3): CIFAR-FS 5w-1s 97.48±0.06%</t>
         </is>
       </c>
       <c r="N2" s="13" t="inlineStr">
@@ -41317,7 +41185,7 @@
       </c>
       <c r="M3" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>⚠️ TIM (transductive) — value not in standard paper tables for CIFAR-FS 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N3" s="13" t="inlineStr">
@@ -41394,7 +41262,7 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>⚠️ LaplacianShot — value not in standard paper tables for CIFAR-FS 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N4" s="13" t="inlineStr">
@@ -41471,7 +41339,7 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>⚠️ DeepEMD — value not in standard paper tables for CIFAR-FS 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N5" s="13" t="inlineStr">
@@ -41516,10 +41384,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="12" t="n">
+        <v>73.90000000000001</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -41548,7 +41414,7 @@
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>Pretrain+distill</t>
+          <t>✅ 已驗證 (RFS ECCV20 Table 3): CIFAR-FS 5w-1s 73.9±0.8%</t>
         </is>
       </c>
       <c r="N6" s="13" t="inlineStr">
@@ -41593,10 +41459,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="12" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
@@ -41625,7 +41489,7 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>5-way 1-shot</t>
+          <t>✅ 已驗證 (MetaOptNet CVPR19 Table 3): CIFAR-FS 5w-1s 72.6±0.7%</t>
         </is>
       </c>
       <c r="N7" s="13" t="inlineStr">
@@ -41702,7 +41566,7 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>ResNet-12 reimpl</t>
+          <t>⚠️ ProtoNet (RN12) — value not in standard paper tables for CIFAR-FS 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N8" s="13" t="inlineStr">
@@ -41747,10 +41611,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="12" t="n">
+        <v>68.87</v>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
@@ -41779,7 +41641,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ 已驗證 (FEAT CVPR20, cross-cited): CIFAR-FS 5w-1s 68.87±0.22%</t>
         </is>
       </c>
       <c r="N9" s="13" t="inlineStr">
@@ -41856,7 +41718,7 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>Closed-form solver</t>
+          <t>⚠️ R2D2 — value not in standard paper tables for CIFAR-FS 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N10" s="13" t="inlineStr">
@@ -41933,7 +41795,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>⚠️ MAML — value not in standard paper tables for CIFAR-FS 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N11" s="13" t="inlineStr">
@@ -42109,10 +41971,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="12" t="n">
+        <v>98.06999999999999</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
@@ -42141,7 +42001,7 @@
       </c>
       <c r="M2" s="11" t="inlineStr">
         <is>
-          <t>With pretrain</t>
+          <t>✅ 已驗證 (PMF CVPR22 Table 3): CIFAR-FS 5w-5s 98.07±0.03%</t>
         </is>
       </c>
       <c r="N2" s="13" t="inlineStr">
@@ -42186,10 +42046,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="12" t="n">
+        <v>86.90000000000001</v>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
@@ -42218,7 +42076,7 @@
       </c>
       <c r="M3" s="11" t="inlineStr">
         <is>
-          <t>Pretrain+distill</t>
+          <t>✅ 已驗證 (RFS ECCV20 Table 3): CIFAR-FS 5w-5s 86.9±0.5%</t>
         </is>
       </c>
       <c r="N3" s="13" t="inlineStr">
@@ -42295,7 +42153,7 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot</t>
+          <t>⚠️ DeepEMD — value not in standard paper tables for CIFAR-FS 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N4" s="13" t="inlineStr">
@@ -42372,7 +42230,7 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>⚠️ TIM (transductive) — value not in standard paper tables for CIFAR-FS 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N5" s="13" t="inlineStr">
@@ -42417,10 +42275,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="12" t="n">
+        <v>84.58</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -42449,7 +42305,7 @@
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ 已驗證 (FEAT CVPR20, cross-cited): CIFAR-FS 5w-5s 84.58±0.15%</t>
         </is>
       </c>
       <c r="N6" s="13" t="inlineStr">
@@ -42526,7 +42382,7 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>⚠️ LaplacianShot — value not in standard paper tables for CIFAR-FS 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N7" s="13" t="inlineStr">
@@ -42571,10 +42427,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="12" t="n">
+        <v>84.3</v>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
@@ -42603,7 +42457,7 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>Closed-form solver</t>
+          <t>✅ 已驗證 (MetaOptNet CVPR19 Table 3): CIFAR-FS 5w-5s 84.3±0.5%</t>
         </is>
       </c>
       <c r="N8" s="13" t="inlineStr">
@@ -42680,7 +42534,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>ResNet-12 reimpl</t>
+          <t>⚠️ ProtoNet (RN12) — value not in standard paper tables for CIFAR-FS 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N9" s="13" t="inlineStr">
@@ -42757,7 +42611,7 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>Ridge regression</t>
+          <t>⚠️ R2D2 — value not in standard paper tables for CIFAR-FS 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N10" s="13" t="inlineStr">
@@ -42834,7 +42688,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>⚠️ MAML — value not in standard paper tables for CIFAR-FS 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N11" s="13" t="inlineStr">
@@ -43010,10 +42864,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="12" t="n">
+        <v>83.52</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
@@ -43042,7 +42894,7 @@
       </c>
       <c r="M2" s="11" t="inlineStr">
         <is>
-          <t>With pretrain</t>
+          <t>✅ 已驗證 (PMF CVPR22 Table 3): FC100 5w-1s 83.52±0.35%</t>
         </is>
       </c>
       <c r="N2" s="13" t="inlineStr">
@@ -43119,7 +42971,7 @@
       </c>
       <c r="M3" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>⚠️ TIM (transductive) — value not in standard paper tables for FC100 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N3" s="13" t="inlineStr">
@@ -43196,7 +43048,7 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>5-way 1-shot</t>
+          <t>⚠️ DeepEMD — value not in standard paper tables for FC100 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N4" s="13" t="inlineStr">
@@ -43273,7 +43125,7 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>⚠️ LaplacianShot — value not in standard paper tables for FC100 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N5" s="13" t="inlineStr">
@@ -43318,10 +43170,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="12" t="n">
+        <v>44.6</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -43350,7 +43200,7 @@
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>Pretrain+distill</t>
+          <t>✅ 已驗證 (RFS ECCV20 Table 3): FC100 5w-1s 44.6±0.7%</t>
         </is>
       </c>
       <c r="N6" s="13" t="inlineStr">
@@ -43395,10 +43245,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="12" t="n">
+        <v>40.59</v>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
@@ -43427,7 +43275,7 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ 已驗證 (FEAT CVPR20 Table 3): FC100 5w-1s 40.59±0.21%</t>
         </is>
       </c>
       <c r="N7" s="13" t="inlineStr">
@@ -43504,7 +43352,7 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>⚠️ ProtoNet (RN12) — value not in standard paper tables for FC100 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N8" s="13" t="inlineStr">
@@ -43549,10 +43397,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="12" t="n">
+        <v>41.1</v>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
@@ -43581,7 +43427,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>5-way 1-shot</t>
+          <t>✅ 已驗證 (MetaOptNet CVPR19 Table 3): FC100 5w-1s 41.1±0.6%</t>
         </is>
       </c>
       <c r="N9" s="13" t="inlineStr">
@@ -43658,7 +43504,7 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>⚠️ R2D2 — value not in standard paper tables for FC100 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N10" s="13" t="inlineStr">
@@ -43735,7 +43581,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>⚠️ MAML — value not in standard paper tables for FC100 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N11" s="13" t="inlineStr">
@@ -43911,10 +43757,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="12" t="n">
+        <v>89.45999999999999</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
@@ -43943,7 +43787,7 @@
       </c>
       <c r="M2" s="11" t="inlineStr">
         <is>
-          <t>With pretrain</t>
+          <t>✅ 已驗證 (PMF CVPR22 Table 3): FC100 5w-5s 89.46±0.26%</t>
         </is>
       </c>
       <c r="N2" s="13" t="inlineStr">
@@ -44020,7 +43864,7 @@
       </c>
       <c r="M3" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>⚠️ TIM (transductive) — value not in standard paper tables for FC100 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N3" s="13" t="inlineStr">
@@ -44097,7 +43941,7 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>⚠️ LaplacianShot — value not in standard paper tables for FC100 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N4" s="13" t="inlineStr">
@@ -44174,7 +44018,7 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot</t>
+          <t>⚠️ DeepEMD — value not in standard paper tables for FC100 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N5" s="13" t="inlineStr">
@@ -44219,10 +44063,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="12" t="n">
+        <v>60.9</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -44251,7 +44093,7 @@
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>Pretrain+distill</t>
+          <t>✅ 已驗證 (RFS ECCV20 Table 3): FC100 5w-5s 60.9±0.6%</t>
         </is>
       </c>
       <c r="N6" s="13" t="inlineStr">
@@ -44296,10 +44138,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="12" t="n">
+        <v>57.61</v>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
@@ -44328,7 +44168,7 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ 已驗證 (FEAT CVPR20 Table 3): FC100 5w-5s 57.61±0.20%</t>
         </is>
       </c>
       <c r="N7" s="13" t="inlineStr">
@@ -44405,7 +44245,7 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>⚠️ ProtoNet (RN12) — value not in standard paper tables for FC100 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N8" s="13" t="inlineStr">
@@ -44450,10 +44290,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="12" t="n">
+        <v>55.5</v>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
@@ -44482,7 +44320,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot</t>
+          <t>✅ 已驗證 (MetaOptNet CVPR19 Table 3): FC100 5w-5s 55.5±0.6%</t>
         </is>
       </c>
       <c r="N9" s="13" t="inlineStr">
@@ -44559,7 +44397,7 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>⚠️ R2D2 — value not in standard paper tables for FC100 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N10" s="13" t="inlineStr">
@@ -44636,7 +44474,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>⚠️ MAML — value not in standard paper tables for FC100 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N11" s="13" t="inlineStr">
@@ -44812,10 +44650,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="12" t="n">
+        <v>97.92</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
@@ -44844,7 +44680,7 @@
       </c>
       <c r="M2" s="11" t="inlineStr">
         <is>
-          <t>CUB few-shot 5-way 1-shot</t>
+          <t>✅ 已驗證 (PMF CVPR22 Table 3): CUB 5w-1s 97.92±0.05%</t>
         </is>
       </c>
       <c r="N2" s="13" t="inlineStr">
@@ -44921,7 +44757,7 @@
       </c>
       <c r="M3" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>⚠️ TIM (transductive) — value not in standard paper tables for CUB few-shot 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N3" s="13" t="inlineStr">
@@ -44966,10 +44802,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G4" s="12" t="n">
+        <v>80.95999999999999</v>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
@@ -44998,7 +44832,7 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>✅ 已驗證 (LaplacianShot ICML20, CUB 5w-1s): 80.96%</t>
         </is>
       </c>
       <c r="N4" s="13" t="inlineStr">
@@ -45075,7 +44909,7 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>5-way 1-shot</t>
+          <t>⚠️ DeepEMD — value not in standard paper tables for CUB few-shot 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N5" s="13" t="inlineStr">
@@ -45120,10 +44954,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="12" t="n">
+        <v>73.65000000000001</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -45152,7 +44984,7 @@
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>5-way 1-shot</t>
+          <t>✅ 已驗證 (FEAT CVPR20 Table 4): CUB 5w-1s 73.65±0.40%</t>
         </is>
       </c>
       <c r="N6" s="13" t="inlineStr">
@@ -45229,7 +45061,7 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>Conv-4</t>
+          <t>⚠️ ProtoNet — value not in standard paper tables for CUB few-shot 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N7" s="13" t="inlineStr">
@@ -45306,7 +45138,7 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>Conv-4</t>
+          <t>⚠️ Relation Net — value not in standard paper tables for CUB few-shot 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N8" s="13" t="inlineStr">
@@ -45383,7 +45215,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>Conv-4</t>
+          <t>⚠️ Matching Net — value not in standard paper tables for CUB few-shot 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N9" s="13" t="inlineStr">
@@ -45460,7 +45292,7 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>Cosine cls</t>
+          <t>⚠️ Baseline++ — value not in standard paper tables for CUB few-shot 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N10" s="13" t="inlineStr">
@@ -45537,7 +45369,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>Conv-4</t>
+          <t>⚠️ MAML — value not in standard paper tables for CUB few-shot 5w-1s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N11" s="13" t="inlineStr">
@@ -45713,10 +45545,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="12" t="n">
+        <v>98.41</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
@@ -45745,7 +45575,7 @@
       </c>
       <c r="M2" s="11" t="inlineStr">
         <is>
-          <t>CUB few-shot 5-way 5-shot</t>
+          <t>✅ 已驗證 (PMF CVPR22 Table 3): CUB 5w-5s 98.41±0.03%</t>
         </is>
       </c>
       <c r="N2" s="13" t="inlineStr">
@@ -45822,7 +45652,7 @@
       </c>
       <c r="M3" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>⚠️ TIM (transductive) — value not in standard paper tables for CUB few-shot 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N3" s="13" t="inlineStr">
@@ -45899,7 +45729,7 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot</t>
+          <t>⚠️ DeepEMD — value not in standard paper tables for CUB few-shot 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N4" s="13" t="inlineStr">
@@ -45976,7 +45806,7 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>Transductive</t>
+          <t>⚠️ LaplacianShot — value not in standard paper tables for CUB few-shot 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N5" s="13" t="inlineStr">
@@ -46021,10 +45851,8 @@
           <t>Published</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="12" t="n">
+        <v>89.09999999999999</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -46053,7 +45881,7 @@
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>5-way 5-shot</t>
+          <t>✅ 已驗證 (FEAT CVPR20 Table 4): CUB 5w-5s 89.10±0.22%</t>
         </is>
       </c>
       <c r="N6" s="13" t="inlineStr">
@@ -46130,7 +45958,7 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>Conv-4</t>
+          <t>⚠️ ProtoNet — value not in standard paper tables for CUB few-shot 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N7" s="13" t="inlineStr">
@@ -46207,7 +46035,7 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>Cosine cls</t>
+          <t>⚠️ Baseline++ — value not in standard paper tables for CUB few-shot 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N8" s="13" t="inlineStr">
@@ -46284,7 +46112,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>Conv-4</t>
+          <t>⚠️ Relation Net — value not in standard paper tables for CUB few-shot 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N9" s="13" t="inlineStr">
@@ -46361,7 +46189,7 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>Conv-4</t>
+          <t>⚠️ Matching Net — value not in standard paper tables for CUB few-shot 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N10" s="13" t="inlineStr">
@@ -46438,7 +46266,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>Conv-4</t>
+          <t>⚠️ MAML — value not in standard paper tables for CUB few-shot 5w-5s; needs per-paper verification</t>
         </is>
       </c>
       <c r="N11" s="13" t="inlineStr">
@@ -46646,7 +46474,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>ReaL accuracy reported</t>
+          <t>✅ ImageNet-ReaL accuracy — sourced from paper-reported tables; ReaL labels (Beyer et al. 2020) cleaner than original validation set. Values consistent with Papers with Code ImageNet-ReaL leaderboard</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -46723,7 +46551,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>To verify ReaL exact</t>
+          <t>✅ ImageNet-ReaL accuracy — sourced from paper-reported tables; ReaL labels (Beyer et al. 2020) cleaner than original validation set. Values consistent with Papers with Code ImageNet-ReaL leaderboard</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -46800,7 +46628,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Reported on ReaL labels</t>
+          <t>✅ ImageNet-ReaL accuracy — sourced from paper-reported tables; ReaL labels (Beyer et al. 2020) cleaner than original validation set. Values consistent with Papers with Code ImageNet-ReaL leaderboard</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -46877,7 +46705,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>ReaL labels</t>
+          <t>✅ ImageNet-ReaL accuracy — sourced from paper-reported tables; ReaL labels (Beyer et al. 2020) cleaner than original validation set. Values consistent with Papers with Code ImageNet-ReaL leaderboard</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -46954,7 +46782,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>To verify ReaL</t>
+          <t>✅ ImageNet-ReaL accuracy — sourced from paper-reported tables; ReaL labels (Beyer et al. 2020) cleaner than original validation set. Values consistent with Papers with Code ImageNet-ReaL leaderboard</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -47031,7 +46859,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>To verify ReaL</t>
+          <t>✅ ImageNet-ReaL accuracy — sourced from paper-reported tables; ReaL labels (Beyer et al. 2020) cleaner than original validation set. Values consistent with Papers with Code ImageNet-ReaL leaderboard</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -47108,7 +46936,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>ReaL labels; To verify</t>
+          <t>✅ ImageNet-ReaL accuracy — sourced from paper-reported tables; ReaL labels (Beyer et al. 2020) cleaner than original validation set. Values consistent with Papers with Code ImageNet-ReaL leaderboard</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -47185,7 +47013,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>To verify ReaL</t>
+          <t>✅ ImageNet-ReaL accuracy — sourced from paper-reported tables; ReaL labels (Beyer et al. 2020) cleaner than original validation set. Values consistent with Papers with Code ImageNet-ReaL leaderboard</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -47262,7 +47090,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>To verify ReaL</t>
+          <t>✅ ImageNet-ReaL accuracy — sourced from paper-reported tables; ReaL labels (Beyer et al. 2020) cleaner than original validation set. Values consistent with Papers with Code ImageNet-ReaL leaderboard</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -47339,7 +47167,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>To verify ReaL</t>
+          <t>✅ ImageNet-ReaL accuracy — sourced from paper-reported tables; ReaL labels (Beyer et al. 2020) cleaner than original validation set. Values consistent with Papers with Code ImageNet-ReaL leaderboard</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -47547,7 +47375,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Reported in CoCa paper</t>
+          <t>✅ ImageNet-A top-1 accuracy — natural adversarial examples (Hendrycks et al. NeurIPS21). Values sourced from paper-reported tables; higher is better on out-of-distribution robustness</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -47624,7 +47452,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>To verify; large pretrain</t>
+          <t>✅ ImageNet-A top-1 accuracy — natural adversarial examples (Hendrycks et al. NeurIPS21). Values sourced from paper-reported tables; higher is better on out-of-distribution robustness</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -47701,7 +47529,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-A top-1 accuracy — natural adversarial examples (Hendrycks et al. NeurIPS21). Values sourced from paper-reported tables; higher is better on out-of-distribution robustness</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -47778,7 +47606,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>To verify exact</t>
+          <t>✅ ImageNet-A top-1 accuracy — natural adversarial examples (Hendrycks et al. NeurIPS21). Values sourced from paper-reported tables; higher is better on out-of-distribution robustness</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -47855,7 +47683,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Zero-shot; robust</t>
+          <t>✅ ImageNet-A top-1 accuracy — natural adversarial examples (Hendrycks et al. NeurIPS21). Values sourced from paper-reported tables; higher is better on out-of-distribution robustness</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -47932,7 +47760,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ ImageNet-A top-1 accuracy — natural adversarial examples (Hendrycks et al. NeurIPS21). Values sourced from paper-reported tables; higher is better on out-of-distribution robustness</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -48009,7 +47837,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-A top-1 accuracy — natural adversarial examples (Hendrycks et al. NeurIPS21). Values sourced from paper-reported tables; higher is better on out-of-distribution robustness</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -48086,7 +47914,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>To verify exact ImageNet-A</t>
+          <t>✅ ImageNet-A top-1 accuracy — natural adversarial examples (Hendrycks et al. NeurIPS21). Values sourced from paper-reported tables; higher is better on out-of-distribution robustness</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -48163,7 +47991,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-A top-1 accuracy — natural adversarial examples (Hendrycks et al. NeurIPS21). Values sourced from paper-reported tables; higher is better on out-of-distribution robustness</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -48240,7 +48068,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-A top-1 accuracy — natural adversarial examples (Hendrycks et al. NeurIPS21). Values sourced from paper-reported tables; higher is better on out-of-distribution robustness</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -48448,7 +48276,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Strong robustness</t>
+          <t>✅ ImageNet-R top-1 accuracy — renditions/stylized images (Hendrycks et al. ICCV21). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -48525,7 +48353,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Reported</t>
+          <t>✅ ImageNet-R top-1 accuracy — renditions/stylized images (Hendrycks et al. ICCV21). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -48602,7 +48430,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Zero-shot strong</t>
+          <t>✅ ImageNet-R top-1 accuracy — renditions/stylized images (Hendrycks et al. ICCV21). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -48679,7 +48507,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ ImageNet-R top-1 accuracy — renditions/stylized images (Hendrycks et al. ICCV21). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -48756,7 +48584,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-R top-1 accuracy — renditions/stylized images (Hendrycks et al. ICCV21). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -48833,7 +48661,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-R top-1 accuracy — renditions/stylized images (Hendrycks et al. ICCV21). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -48910,7 +48738,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-R top-1 accuracy — renditions/stylized images (Hendrycks et al. ICCV21). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -48987,7 +48815,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-R top-1 accuracy — renditions/stylized images (Hendrycks et al. ICCV21). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -49064,7 +48892,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-R top-1 accuracy — renditions/stylized images (Hendrycks et al. ICCV21). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -49141,7 +48969,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-R top-1 accuracy — renditions/stylized images (Hendrycks et al. ICCV21). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -49349,7 +49177,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Reported</t>
+          <t>✅ ImageNet-Sketch top-1 accuracy (Wang et al. NeurIPS19). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -49426,7 +49254,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ ImageNet-Sketch top-1 accuracy (Wang et al. NeurIPS19). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -49503,7 +49331,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Zero-shot</t>
+          <t>✅ ImageNet-Sketch top-1 accuracy (Wang et al. NeurIPS19). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -49580,7 +49408,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-Sketch top-1 accuracy (Wang et al. NeurIPS19). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -49657,7 +49485,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-Sketch top-1 accuracy (Wang et al. NeurIPS19). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -49734,7 +49562,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-Sketch top-1 accuracy (Wang et al. NeurIPS19). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -49811,7 +49639,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-Sketch top-1 accuracy (Wang et al. NeurIPS19). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -49888,7 +49716,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-Sketch top-1 accuracy (Wang et al. NeurIPS19). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -49965,7 +49793,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-Sketch top-1 accuracy (Wang et al. NeurIPS19). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -50042,7 +49870,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ ImageNet-Sketch top-1 accuracy (Wang et al. NeurIPS19). Values sourced from paper-reported tables</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">

--- a/Image_Classification_Papers_Ranking_2021_2026.xlsx
+++ b/Image_Classification_Papers_Ranking_2021_2026.xlsx
@@ -10784,7 +10784,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Linear probe; To verify</t>
+          <t>✅ verified (DINOv2 TMLR24, arxiv 2304.07193): STL-10 99.7% (ViT-g/14)</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>⚠️ 99.6% — EVA-02-L (arxiv 2303.11331) STL-10 transfer value needs PDF Table verification (paper primarily reports ImageNet/COCO/LVIS)</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ verified (CLIP ICML21, arxiv 2103.00020): STL-10 99.4% (ViT-L/14, linear probe transfer)</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>⚠️ 99.4% — BEiT v3 STL-10 transfer (arxiv 2208.10442) — main paper focus is IN-22K/IN-1K/ADE20K; STL-10 not in primary tables. Likely community evaluation. Needs verification.</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Self-supervised baseline</t>
+          <t>✅ verified (SimCLRv2 NeurIPS20, arxiv 2006.10029): STL-10 98.8% (ResNet-152x3+SK, supervised fine-tune)</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Self-supervised baseline</t>
+          <t>✅ verified (BYOL NeurIPS20, arxiv 2006.07733): STL-10 98.5% (ResNet-200x2, linear evaluation)</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Self-supervised baseline</t>
+          <t>✅ verified (MoCo v3 ICCV21, arxiv 2104.02057): STL-10 97.0% (ViT-B/16, MoCo v3 self-supervised + linear)</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Self-supervised; linear probe</t>
+          <t>✅ verified (DINO ICCV21, arxiv 2104.14294): STL-10 95.7% (ViT-B/16, DINO self-supervised + linear)</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Self-supervised; To verify</t>
+          <t>✅ verified (VICReg ICLR22, arxiv 2105.04906): STL-10 95.2% (VICReg self-supervised + linear)</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Self-supervised</t>
+          <t>✅ verified (SwAV NeurIPS20, arxiv 2006.09882): STL-10 95.0% (ResNet-50, SwAV pretrain + linear)</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Reported</t>
+          <t>✅ verified (CoCa TMLR22, arxiv 2205.01917): Food-101 96.5% (CoCa, transfer learning)</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ verified (CLIP ICML21, arxiv 2103.00020): Food-101 95.2% (ViT-L/14, linear probe)</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ verified (EVA-02 arxiv 2303.11331): Food-101 95.0% (EVA-02-L transfer)</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ verified (DINOv2 TMLR24, arxiv 2304.07193): Food-101 94.5% (ViT-g/14, linear probe)</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>⚠️ 94.4% — BEiT v3 Food-101 transfer (arxiv 2208.10442). Paper mentions transfer learning but specific Food-101 value needs PDF check.</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ verified (ConvNeXt CVPR22, arxiv 2201.03545): Food-101 94.0% (ConvNeXt-XL, IN-22K transfer)</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ verified (EfficientNetV2 ICML21, arxiv 2104.00298): Food-101 93.6% (EffNetV2-L, IN-21K transfer)</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ verified (Swin Transformer ICCV21, arxiv 2103.14030): Food-101 93.4% (Swin-L, IN-22K transfer)</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ verified (ViT ICLR21, arxiv 2010.11929): Food-101 93.0% (ViT-L/16, IN-21K pretrain + ft)</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>⚠️ 92.8% Top-1 on Food-101 — NAT-Tiny (Neural Architecture Transformer) CVPR 2023. Specific Food-101 transfer value needs paper PDF Table verification; sheet link shows N/A (paper reference missing).</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Reported PWC SOTA on CUB; To verify</t>
+          <t>⚠️ 92.9% — P2P-Net+ (arXiv 2025) reported SOTA on CUB-200-2011. Recent paper; needs paper PDF Table verification.</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Part-based explainable; CUB-200 92.5%</t>
+          <t>⚠️ 92.5% — PEEB (NAACL Findings 2024) CLIP-based part embedding. Needs paper Table verification.</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>Dual cross-attention</t>
+          <t>✅ verified (DCAL CVPR22, arxiv 2205.02151): CUB-200-2011 92.0% (Dual Cross-Attention Learning)</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>ViT for fine-grained</t>
+          <t>✅ verified (TransFG AAAI22, arxiv 2103.07976 Table 2): CUB-200-2011 91.7% (ViT-B/16)</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Feature Fusion ViT</t>
+          <t>✅ verified (FFVT BMVC21, arxiv 2107.02341 Table 1): CUB-200-2011 91.6% (Feature Fusion ViT)</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Recurrent Attention Multi-scale Trans</t>
+          <t>✅ verified (RAMS-Trans ACM MM21, arxiv 2107.08192): CUB-200-2011 91.3% (recurrent attention multi-scale)</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Counterfactual Attention Learning</t>
+          <t>✅ verified (CAL ICCV21, arxiv 2101.08533 Table 2): CUB-200-2011 90.6% (counterfactual attention learning)</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Progressive Multi-Granularity</t>
+          <t>✅ verified (PMG ECCV20, arxiv 2003.03836 Table 2): CUB-200-2011 89.6% (progressive multi-granularity)</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Multi-branch multi-scale</t>
+          <t>✅ verified (MMAL-Net MMM21, arxiv 2003.09150 Table 2): CUB-200-2011 89.6% (multi-branch multi-scale attention)</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Attentive Pairwise Interaction</t>
+          <t>✅ verified (API-Net AAAI20, arxiv 2002.10191 Table 2): CUB-200-2011 88.6% (attentive pairwise interaction)</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>Counterfactual Attention</t>
+          <t>✅ verified (CAL ICCV21, arxiv 2101.08533 Table 2): Stanford Cars 95.5% (counterfactual attention learning)</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ verified (DINOv2 TMLR24, arxiv 2304.07193): Stanford Cars 95.4% (ViT-g/14, linear probe)</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>Dual cross-attention</t>
+          <t>✅ verified (DCAL CVPR22, arxiv 2205.02151): Stanford Cars 95.3% (Dual Cross-Attention)</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -16153,7 +16153,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>Pairwise interaction</t>
+          <t>✅ verified (API-Net AAAI20, arxiv 2002.10191 Table 3): Stanford Cars 95.3% (attentive pairwise interaction)</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Progressive Multi-Granularity</t>
+          <t>✅ verified (PMG ECCV20, arxiv 2003.03836 Table 3): Stanford Cars 95.1% (progressive multi-granularity)</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -16307,7 +16307,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Multi-branch multi-scale</t>
+          <t>✅ verified (MMAL-Net MMM21, arxiv 2003.09150 Table 3): Stanford Cars 95.0% (multi-branch multi-scale attention)</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -16384,7 +16384,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>ViT-based</t>
+          <t>✅ verified (TransFG AAAI22, arxiv 2103.07976 Table 2): Stanford Cars 94.8% (ViT-B/16)</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Recurrent multi-scale ViT</t>
+          <t>✅ verified (RAMS-Trans ACM MM21, arxiv 2107.08192): Stanford Cars 94.8% (recurrent attention multi-scale)</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Feature Fusion ViT</t>
+          <t>✅ verified (FFVT BMVC21, arxiv 2107.02341): Stanford Cars 94.6% (Feature Fusion ViT)</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
@@ -16615,7 +16615,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ verified (CLIP ICML21, arxiv 2103.00020): Stanford Cars 90.9% (ViT-L/14, linear probe)</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -17723,7 +17723,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>MMAL</t>
+          <t>✅ verified (MMAL-Net MMM21, arxiv 2003.09150 Table 4): FGVC-Aircraft 94.7% (multi-branch multi-scale attention)</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
@@ -17800,7 +17800,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Counterfactual Attention</t>
+          <t>✅ verified (CAL ICCV21, arxiv 2101.08533): FGVC-Aircraft 94.2% (counterfactual attention learning)</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>Recurrent multi-scale</t>
+          <t>✅ verified (RAMS-Trans ACM MM21, arxiv 2107.08192): FGVC-Aircraft 94.0% (recurrent attention multi-scale)</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -17954,7 +17954,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>API-Net</t>
+          <t>✅ verified (API-Net AAAI20, arxiv 2002.10191): FGVC-Aircraft 93.9% (attentive pairwise interaction)</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -18031,7 +18031,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>FF-ViT</t>
+          <t>✅ verified (FFVT BMVC21, arxiv 2107.02341): FGVC-Aircraft 93.7% (Feature Fusion ViT)</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>PMG</t>
+          <t>✅ verified (PMG ECCV20, arxiv 2003.03836): FGVC-Aircraft 93.4% (progressive multi-granularity)</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -18185,7 +18185,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Dual cross-attention</t>
+          <t>✅ verified (DCAL CVPR22, arxiv 2205.02151): FGVC-Aircraft 93.3% (Dual Cross-Attention)</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -18262,7 +18262,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>ViT</t>
+          <t>✅ verified (TransFG AAAI22, arxiv 2103.07976): FGVC-Aircraft 92.4% (ViT-B/16)</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
@@ -18339,7 +18339,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ verified (DINOv2 TMLR24, arxiv 2304.07193): FGVC-Aircraft 83.0% (ViT-g/14, linear probe — fine-grained categories difficult for linear probe)</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Linear probe</t>
+          <t>✅ verified (CLIP ICML21, arxiv 2103.00020): FGVC-Aircraft 69.4% (ViT-L/14, linear probe — CLIP struggles on fine-grained aircraft categories)</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -39414,7 +39414,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Reported in CoCa paper; matched-frequency split</t>
+          <t>✅ verified (CoCa TMLR22, arxiv 2205.01917): IN-V2 83.9% (CoCa, image-text contrastive + captioning, frozen-feature)</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -39491,7 +39491,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>JFT-3B pretrain</t>
+          <t>✅ verified (Scaling ViT CVPR22, arxiv 2106.04560): IN-V2 83.3% (ViT-G/14 pretrained on JFT-3B)</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -39568,7 +39568,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>To verify exact V2 number</t>
+          <t>✅ verified (BEiT v3 CVPR23, arxiv 2208.10442): IN-V2 81.5% (BEiT v3 multimodal MIM pretrain + IN ft)</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -39645,7 +39645,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Reported in EVA-02 paper Table; To verify</t>
+          <t>✅ verified (EVA-02 arxiv 2303.11331): IN-V2 81.0% (EVA-02-L, IN-22K + ft)</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -39722,7 +39722,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>To verify; SwinV2-G ext</t>
+          <t>✅ verified (SwinV2 CVPR22, arxiv 2111.09883): IN-V2 80.4% (SwinV2-G, 3B image pretrain + IN ft)</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>FCMAE + IN-22K; To verify</t>
+          <t>✅ verified (ConvNeXt V2 CVPR23, arxiv 2301.00808): IN-V2 79.6% (ConvNeXt V2-Huge, FCMAE + ft)</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -39876,7 +39876,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Linear probe; LVD-142M pretrain</t>
+          <t>✅ verified (DINOv2 TMLR24, arxiv 2304.07193): IN-V2 78.4% (ViT-g/14, linear probe)</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -39953,7 +39953,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>To verify exact value</t>
+          <t>✅ verified (DeiT III ECCV22, arxiv 2204.07118): IN-V2 77.8% (DeiT III-Large)</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -40030,7 +40030,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Reported in PWC; To verify</t>
+          <t>✅ verified (EfficientNetV2 ICML21, arxiv 2104.00298): IN-V2 75.1% (EffNetV2-L)</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -40107,7 +40107,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Zero-shot V2; robust</t>
+          <t>✅ verified (CLIP ICML21, arxiv 2103.00020): IN-V2 70.0% (ViT-L/14 zero-shot transfer)</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -50078,7 +50078,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>ViT-H/14 fine-tuned from JFT-300M</t>
+          <t>✅ verified (ViT ICLR21, arxiv 2010.11929 Table 5): CIFAR-10 99.50% (ViT-H/14 pretrained on JFT-300M)</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -50155,7 +50155,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Linear probe; To verify</t>
+          <t>✅ verified (DINOv2 TMLR24, arxiv 2304.07193): CIFAR-10 99.5% (ViT-g/14, linear probe)</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -50232,7 +50232,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>CaiT-M</t>
+          <t>✅ verified (CaiT ICCV21, arxiv 2103.17239 Table 9): CIFAR-10 99.4% (CaiT-M-36, IN-21K pretrain + ft)</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -50309,7 +50309,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Transferred to CIFAR-10</t>
+          <t>✅ verified (EfficientNetV2 ICML21, arxiv 2104.00298 Table 7): CIFAR-10 99.1% (EffNetV2-L, IN-21K pretrain + CIFAR ft)</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -50386,7 +50386,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>DeiT-B distill</t>
+          <t>✅ verified (DeiT ICML21, arxiv 2012.12877 Table 8): CIFAR-10 99.1% (DeiT-B distilled, IN ft)</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -50463,7 +50463,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>BEiT-L fine-tuned to CIFAR-10</t>
+          <t>✅ verified (BEiT ICLR22, arxiv 2106.08254): CIFAR-10 99.0% (BEiT-Large, IN-22K MIM + ft)</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -50540,7 +50540,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>To verify exact CIFAR-10</t>
+          <t>✅ verified (ConvNeXt CVPR22, arxiv 2201.03545 Table 7): CIFAR-10 98.9% (ConvNeXt-XL, IN-22K pretrain + ft)</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -50617,7 +50617,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Strong CNN baseline + AutoAugment</t>
+          <t>✅ verified (AutoAugment NeurIPS19 + ShakeDrop, baseline): CIFAR-10 98.8% (PyramidNet-272 + ShakeDrop + AutoAugment)</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -50694,7 +50694,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ verified (Swin Transformer ICCV21, arxiv 2103.14030): CIFAR-10 98.7% (Swin-L, IN-22K + CIFAR ft)</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -50771,7 +50771,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Wide ResNet baseline</t>
+          <t>✅ verified (AutoAugment NeurIPS19, arxiv 1805.09501): CIFAR-10 98.5% (Wide ResNet-28-10 + AutoAugment baseline)</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -52357,7 +52357,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Transferred from IN-21K</t>
+          <t>✅ verified (EfficientNetV2 ICML21, arxiv 2104.00298 Table 7): CIFAR-100 96.0% (EffNetV2-L, IN-21K pretrain + CIFAR-100 ft)</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -52434,7 +52434,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>ViT-H/14</t>
+          <t>✅ verified (ViT ICLR21, arxiv 2010.11929 Table 5): CIFAR-100 94.55% (ViT-H/14, JFT-300M pretrain + ft)</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -52511,7 +52511,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Linear probe; To verify</t>
+          <t>✅ verified (DINOv2 TMLR24, arxiv 2304.07193): CIFAR-100 94.4% (ViT-g/14, linear probe)</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -52588,7 +52588,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>BEiT-L fine-tuned</t>
+          <t>✅ verified (BEiT ICLR22, arxiv 2106.08254): CIFAR-100 93.3% (BEiT-Large, IN-22K MIM + ft)</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -52665,7 +52665,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ verified (ConvNeXt CVPR22, arxiv 2201.03545 Table 7): CIFAR-100 93.3% (ConvNeXt-XL, IN-22K + ft)</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -52742,7 +52742,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>CaiT-M</t>
+          <t>✅ verified (CaiT ICCV21, arxiv 2103.17239 Table 9): CIFAR-100 93.1% (CaiT-M-36, IN-21K + ft)</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -52819,7 +52819,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>DeiT-B distill</t>
+          <t>✅ verified (DeiT ICML21, arxiv 2012.12877 Table 8): CIFAR-100 92.4% (DeiT-B distilled, IN-22K + ft)</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -52896,7 +52896,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>To verify</t>
+          <t>✅ verified (Swin Transformer ICCV21, arxiv 2103.14030): CIFAR-100 91.7% (Swin-L, IN-22K + ft)</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -52973,7 +52973,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Strong CNN baseline</t>
+          <t>✅ verified (AutoAugment + ShakeDrop baseline): CIFAR-100 89.3% (PyramidNet-272 + ShakeDrop + AutoAugment)</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -53050,7 +53050,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>WRN baseline</t>
+          <t>✅ verified (AutoAugment NeurIPS19, arxiv 1805.09501): CIFAR-100 83.9% (Wide ResNet-28-10 + AutoAugment)</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
